--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -116,12 +116,6 @@
   </si>
   <si>
     <t>Apertura pedido</t>
-  </si>
-  <si>
-    <t>1216803782989477</t>
-  </si>
-  <si>
-    <t>Alcance del proyecto</t>
   </si>
   <si>
     <t xml:space="preserve">Buen día,
@@ -147,6 +141,12 @@
 ·       Se adjunta plano motor.
     Fecha de entrega: 01-09-2026
  </t>
+  </si>
+  <si>
+    <t>1216803782989477</t>
+  </si>
+  <si>
+    <t>Alcance del proyecto</t>
   </si>
   <si>
     <t>1216803782991703</t>
@@ -1841,7 +1841,7 @@
         <v>46232.53939449074</v>
       </c>
       <c r="D6" s="5">
-        <v>46232.53940949074</v>
+        <v>46237.83098412037</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1863,7 +1863,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1895,7 +1895,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9">
         <v>46225.86158383102</v>
@@ -1907,7 +1907,7 @@
         <v>46232.53966210649</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
@@ -1926,7 +1926,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>26</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -297,57 +297,60 @@
     <t>Generación OC corte laser   OT 4381 ,Propuesta compras:</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1216803882357645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Corte plasma   OT 4381  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion OC Corte plasma   OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803882366017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa   OT 4381  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparacion materiales  OT 4381  </t>
+  </si>
+  <si>
+    <t>1216803882366035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Mecanizado  OT 4381  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC mecanizado  OT 4381 </t>
+  </si>
+  <si>
+    <t>1216769310026838</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte Laser   OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803882368171</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC corte laser   OT 4381 ,Fabricacion corte laser  OT 4381 </t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
-    <t>1216803882357645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Corte plasma   OT 4381  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion OC Corte plasma   OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803882366017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa   OT 4381  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparacion materiales  OT 4381  </t>
-  </si>
-  <si>
-    <t>1216803882366035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Mecanizado  OT 4381  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC mecanizado  OT 4381 </t>
-  </si>
-  <si>
-    <t>1216769310026838</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte Laser   OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803882368171</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC corte laser   OT 4381 ,Fabricacion corte laser  OT 4381 </t>
-  </si>
-  <si>
     <t>1216803783052320</t>
   </si>
   <si>
@@ -496,9 +499,6 @@
   </si>
   <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1216803961645389</t>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46225.86582702547</v>
+        <v>46238.48727704861</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>68</v>
@@ -2542,7 +2542,7 @@
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="U17" s="12" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46225.865880763886</v>
+        <v>46238.48727760417</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2605,7 +2605,7 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
+      <c r="U18" s="12" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46225.86597293981</v>
+        <v>46238.4872778125</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>77</v>
@@ -2668,7 +2668,7 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="U19" s="12" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46225.86600605324</v>
+        <v>46238.487277314816</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2731,7 +2731,7 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="11" t="s">
+      <c r="U20" s="12" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2842,12 +2842,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="9">
         <v>46225.86167825232</v>
@@ -2857,7 +2857,7 @@
         <v>46225.86694637731</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2890,7 +2890,7 @@
         <v>68</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2901,12 +2901,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46225.86168543981</v>
@@ -2916,7 +2916,7 @@
         <v>46225.867042893515</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2946,10 +2946,10 @@
         <v>84</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2960,12 +2960,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" s="9">
         <v>46225.86169273148</v>
@@ -2975,7 +2975,7 @@
         <v>46225.86610908565</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3005,7 +3005,7 @@
         <v>83</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3023,12 +3023,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46225.86169921297</v>
@@ -3065,13 +3065,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="9">
         <v>46225.86170601852</v>
@@ -3091,7 +3091,7 @@
         <v>46225.8671391088</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46225.86175964121</v>
@@ -3144,7 +3144,7 @@
         <v>46225.86617241898</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3174,7 +3174,7 @@
         <v>83</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3192,12 +3192,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="9">
         <v>46225.861767326394</v>
@@ -3234,13 +3234,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>80</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46225.8617740162</v>
@@ -3260,7 +3260,7 @@
         <v>46225.86721106482</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3287,13 +3287,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="9">
         <v>46225.86178056713</v>
@@ -3313,16 +3313,16 @@
         <v>46225.866204108796</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3343,7 +3343,7 @@
         <v>83</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3361,12 +3361,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46225.8617949537</v>
@@ -3376,16 +3376,16 @@
         <v>46237.553715648144</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3403,13 +3403,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="9">
         <v>46225.86180262732</v>
@@ -3429,16 +3429,16 @@
         <v>46225.86759815972</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3456,13 +3456,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46225.8618097338</v>
@@ -3482,16 +3482,16 @@
         <v>46225.867627534724</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3509,13 +3509,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3525,17 +3525,17 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B35" s="9">
         <v>46225.86181672454</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46232.575276284726</v>
+        <v>46238.48726621528</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3559,7 +3559,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46225.86182068287</v>
@@ -3584,16 +3584,16 @@
         <v>46235.207714502314</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3611,13 +3611,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>47</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3637,26 +3637,28 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="9">
         <v>46225.86182918982</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9">
+        <v>46238.48719537037</v>
+      </c>
       <c r="D37" s="9">
-        <v>46234.19560074074</v>
+        <v>46238.48721753473</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3674,13 +3676,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3689,13 +3691,13 @@
         <v>46237</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="T37" s="10">
-        <v>0</v>
-      </c>
-      <c r="U37" s="12" t="s">
-        <v>139</v>
+        <v>1</v>
+      </c>
+      <c r="U37" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3705,9 +3707,11 @@
       <c r="B38" s="5">
         <v>46225.86183666666</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46238.487247916666</v>
+      </c>
       <c r="D38" s="5">
-        <v>46237.17126307871</v>
+        <v>46238.48726421296</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>70</v>
@@ -3737,10 +3741,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>143</v>
@@ -3752,13 +3756,13 @@
         <v>46244</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="T38" s="6">
-        <v>0</v>
-      </c>
-      <c r="U38" s="11" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="U38" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3800,13 +3804,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>148</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3821,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4115,7 +4119,7 @@
         <v>158</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>164</v>
@@ -4133,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4178,7 +4182,7 @@
         <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>167</v>
@@ -4196,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4241,7 +4245,7 @@
         <v>158</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>170</v>
@@ -4259,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4280,10 +4284,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4322,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4343,10 +4347,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I49" s="9">
         <v>46261</v>
@@ -4385,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4406,10 +4410,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4448,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4558,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4621,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4633,7 +4637,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46225.87051350695</v>
+        <v>46238.487257870365</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>150</v>
@@ -4686,7 +4690,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46225.8705225</v>
+        <v>46238.48725839121</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>150</v>
@@ -4739,7 +4743,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46225.8705300463</v>
+        <v>46238.48725583333</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>150</v>
@@ -4854,10 +4858,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -4896,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4908,7 +4912,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46225.870570011575</v>
+        <v>46238.487258877314</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>150</v>
@@ -4917,10 +4921,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I59" s="9">
         <v>46274</v>
@@ -4961,7 +4965,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46225.87057787037</v>
+        <v>46238.48726738426</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>150</v>
@@ -4970,10 +4974,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I60" s="5">
         <v>46274</v>
@@ -5014,7 +5018,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46225.87058641204</v>
+        <v>46238.48725643518</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>150</v>
@@ -5023,10 +5027,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I61" s="9">
         <v>46274</v>
@@ -5076,10 +5080,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5218,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5281,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5344,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5505,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5780,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5792,7 +5796,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46225.870697754624</v>
+        <v>46238.48726658565</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>150</v>
@@ -5843,7 +5847,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46225.87070481481</v>
+        <v>46238.487257326386</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>150</v>
@@ -5894,7 +5898,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46225.870712222226</v>
+        <v>46238.48726778935</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>150</v>
@@ -6047,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6322,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6334,7 +6338,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46225.870837442126</v>
+        <v>46238.48726703704</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>150</v>
@@ -6387,7 +6391,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46225.87084591435</v>
+        <v>46238.48725680556</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>150</v>
@@ -6597,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6872,7 +6876,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7194,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7469,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7744,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="U110" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -8019,7 +8023,7 @@
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8341,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="U121" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -8404,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="U122" s="11" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -297,6 +297,9 @@
     <t>Generación OC corte laser   OT 4381 ,Propuesta compras:</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
@@ -496,9 +499,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos  OT 4381 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216803961645389</t>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46238.48727704861</v>
+        <v>46239.186343124995</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>68</v>
@@ -2536,29 +2536,29 @@
       <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>32</v>
+      <c r="S17" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46225.86165034722</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46238.48727760417</v>
+        <v>46239.186343124995</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2591,7 +2591,7 @@
         <v>70</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2599,29 +2599,29 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>32</v>
+      <c r="S18" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="9">
         <v>46225.86165694444</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46238.4872778125</v>
+        <v>46239.18634349537</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2654,7 +2654,7 @@
         <v>70</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="9">
         <v>46246</v>
@@ -2662,29 +2662,29 @@
       <c r="R19" s="9">
         <v>46245</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>32</v>
+      <c r="S19" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5">
         <v>46225.86166292824</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46238.487277314816</v>
+        <v>46239.18634339121</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2717,7 +2717,7 @@
         <v>70</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q20" s="5">
         <v>46246</v>
@@ -2725,19 +2725,19 @@
       <c r="R20" s="5">
         <v>46245</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>32</v>
+      <c r="S20" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" s="9">
         <v>46225.861460914355</v>
@@ -2747,7 +2747,7 @@
         <v>46225.86191712963</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2771,7 +2771,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5">
         <v>46225.86167002315</v>
@@ -2794,16 +2794,16 @@
         <v>46225.8660337037</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2821,13 +2821,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q22" s="5">
         <v>46259</v>
@@ -2842,12 +2842,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="9">
         <v>46225.86167825232</v>
@@ -2857,16 +2857,16 @@
         <v>46225.86694637731</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I23" s="9">
         <v>46247</v>
@@ -2884,13 +2884,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>68</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2901,12 +2901,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46225.86168543981</v>
@@ -2916,16 +2916,16 @@
         <v>46225.867042893515</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I24" s="5">
         <v>46251</v>
@@ -2943,13 +2943,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2960,12 +2960,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="9">
         <v>46225.86169273148</v>
@@ -2975,16 +2975,16 @@
         <v>46225.86610908565</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I25" s="9">
         <v>46247</v>
@@ -3002,10 +3002,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3023,12 +3023,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46225.86169921297</v>
@@ -3038,16 +3038,16 @@
         <v>46225.86712378472</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I26" s="5">
         <v>46247</v>
@@ -3065,13 +3065,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B27" s="9">
         <v>46225.86170601852</v>
@@ -3091,16 +3091,16 @@
         <v>46225.8671391088</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I27" s="9">
         <v>46251</v>
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" s="5">
         <v>46225.86175964121</v>
@@ -3144,16 +3144,16 @@
         <v>46225.86617241898</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3171,10 +3171,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3192,12 +3192,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" s="9">
         <v>46225.861767326394</v>
@@ -3207,16 +3207,16 @@
         <v>46225.86719211805</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I29" s="9">
         <v>46247</v>
@@ -3234,13 +3234,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5">
         <v>46225.8617740162</v>
@@ -3260,16 +3260,16 @@
         <v>46225.86721106482</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I30" s="5">
         <v>46251</v>
@@ -3287,13 +3287,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="9">
         <v>46225.86178056713</v>
@@ -3313,16 +3313,16 @@
         <v>46225.866204108796</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3340,10 +3340,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3361,12 +3361,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46225.8617949537</v>
@@ -3376,16 +3376,16 @@
         <v>46237.553715648144</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3403,13 +3403,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B33" s="9">
         <v>46225.86180262732</v>
@@ -3429,16 +3429,16 @@
         <v>46225.86759815972</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3456,13 +3456,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46225.8618097338</v>
@@ -3482,16 +3482,16 @@
         <v>46225.867627534724</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3509,13 +3509,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3525,7 +3525,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="9">
         <v>46225.86181672454</v>
@@ -3535,7 +3535,7 @@
         <v>46238.48726621528</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3559,7 +3559,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46225.86182068287</v>
@@ -3584,16 +3584,16 @@
         <v>46235.207714502314</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3611,13 +3611,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>47</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="9">
         <v>46225.86182918982</v>
@@ -3649,16 +3649,16 @@
         <v>46238.48721753473</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3676,13 +3676,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3691,7 +3691,7 @@
         <v>46237</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>
@@ -3741,10 +3741,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>143</v>
@@ -3756,7 +3756,7 @@
         <v>46244</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -3804,13 +3804,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>148</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4119,7 +4119,7 @@
         <v>158</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>164</v>
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4182,7 +4182,7 @@
         <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>167</v>
@@ -4200,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4245,7 +4245,7 @@
         <v>158</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>170</v>
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4284,10 +4284,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4347,10 +4347,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I49" s="9">
         <v>46261</v>
@@ -4389,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4410,10 +4410,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4452,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4514,7 +4514,7 @@
         <v>46225.867920069446</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4544,7 +4544,7 @@
         <v>180</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>185</v>
@@ -4562,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4625,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4829,7 +4829,7 @@
         <v>187</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>193</v>
@@ -4858,10 +4858,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -4900,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4921,10 +4921,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I59" s="9">
         <v>46274</v>
@@ -4974,10 +4974,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I60" s="5">
         <v>46274</v>
@@ -5027,10 +5027,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I61" s="9">
         <v>46274</v>
@@ -5080,10 +5080,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5222,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5509,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5784,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6051,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6326,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6876,7 +6876,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7473,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7748,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="U110" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -8023,7 +8023,7 @@
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8345,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="U121" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -8408,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="U122" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="334">
   <si>
     <t>50001582 - "XEMORTIZ LA CANTERA"</t>
   </si>
@@ -744,157 +744,145 @@
     <t>Montaje Rodete OT 4381,Montaje motor OT 4381,Montaje Alabe OT 4381 ,Revestimiento OT 4381</t>
   </si>
   <si>
-    <t>1216991376680218</t>
-  </si>
-  <si>
-    <t>Conexión eléctrica OT 4381</t>
+    <t>1216803961866118</t>
+  </si>
+  <si>
+    <t>Revestimiento OT 4381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje:,Montaje Alabe OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803961867347</t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Revestimiento OT 4381</t>
+  </si>
+  <si>
+    <t>1216803882738266</t>
+  </si>
+  <si>
+    <t>Revestimiento OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803882738289</t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Revestimiento OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803855271786</t>
+  </si>
+  <si>
+    <t>Revestimiento OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216804003110119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje Alabe OT 4381 </t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Revestimiento OT 4381</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Rodete OT 4381</t>
+  </si>
+  <si>
+    <t>1216803855274627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Recepcion Alabe OT 4381 ,Check Planos  OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje Alabe OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803961890296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Planos  OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Recepcion Alabe OT 4381 </t>
+  </si>
+  <si>
+    <t>Montaje Alabe OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803855284220</t>
+  </si>
+  <si>
+    <t>1216804003116105</t>
+  </si>
+  <si>
+    <t>1216804003144681</t>
+  </si>
+  <si>
+    <t>Montaje Rodete OT 4381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje Alabe OT 4381 </t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje motor OT 4381</t>
+  </si>
+  <si>
+    <t>1216803783458328</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje Rodete OT 4381</t>
+  </si>
+  <si>
+    <t>1216804003148414</t>
+  </si>
+  <si>
+    <t>Montaje Rodete OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803783466971</t>
+  </si>
+  <si>
+    <t>1216803961972491</t>
+  </si>
+  <si>
+    <t>1216803783487152</t>
   </si>
   <si>
     <t>Montaje motor OT 4381</t>
   </si>
   <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje Rodete OT 4381</t>
+  </si>
+  <si>
+    <t>1216803961998137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion motor OT 4381 ,Check Planos  OT 4381 </t>
+  </si>
+  <si>
+    <t>Montaje motor OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803961998165</t>
+  </si>
+  <si>
+    <t>1216803783491955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Recepcion motor OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803783517771</t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje motor OT 4381</t>
+  </si>
+  <si>
+    <t>1216803962019545</t>
+  </si>
+  <si>
     <t>Pruebas FAT OT 4381</t>
-  </si>
-  <si>
-    <t>1216803961866118</t>
-  </si>
-  <si>
-    <t>Revestimiento OT 4381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje:,Montaje Alabe OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803961867347</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Revestimiento OT 4381</t>
-  </si>
-  <si>
-    <t>1216803882738266</t>
-  </si>
-  <si>
-    <t>Revestimiento OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803882738289</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Revestimiento OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803855271786</t>
-  </si>
-  <si>
-    <t>Revestimiento OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216804003110119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje Alabe OT 4381 </t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Revestimiento OT 4381</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Rodete OT 4381</t>
-  </si>
-  <si>
-    <t>1216803855274627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Recepcion Alabe OT 4381 ,Check Planos  OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje Alabe OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803961890296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Planos  OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Recepcion Alabe OT 4381 </t>
-  </si>
-  <si>
-    <t>Montaje Alabe OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803855284220</t>
-  </si>
-  <si>
-    <t>1216804003116105</t>
-  </si>
-  <si>
-    <t>1216804003144681</t>
-  </si>
-  <si>
-    <t>Montaje Rodete OT 4381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje Alabe OT 4381 </t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje motor OT 4381</t>
-  </si>
-  <si>
-    <t>1216803783458328</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje Rodete OT 4381</t>
-  </si>
-  <si>
-    <t>1216804003148414</t>
-  </si>
-  <si>
-    <t>Montaje Rodete OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803783466971</t>
-  </si>
-  <si>
-    <t>1216803961972491</t>
-  </si>
-  <si>
-    <t>1216803783487152</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje Rodete OT 4381</t>
-  </si>
-  <si>
-    <t>Montaje:,Conexión eléctrica OT 4381</t>
-  </si>
-  <si>
-    <t>1216803961998137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion motor OT 4381 ,Check Planos  OT 4381 </t>
-  </si>
-  <si>
-    <t>Montaje motor OT 4381,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803961998165</t>
-  </si>
-  <si>
-    <t>1216803783491955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Recepcion motor OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803783517771</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Montaje motor OT 4381</t>
-  </si>
-  <si>
-    <t>1216803962019545</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Conexión eléctrica OT 4381</t>
   </si>
   <si>
     <t xml:space="preserve">RE-PINTADO OT 4381 </t>
@@ -1616,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U122"/>
+  <dimension ref="A1:U121"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5403,11 +5391,11 @@
         <v>221</v>
       </c>
       <c r="B68" s="5">
-        <v>46232.60331190973</v>
+        <v>46225.862226516205</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46232.62438318287</v>
+        <v>46232.62438219908</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>222</v>
@@ -5416,14 +5404,16 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
+        <v>56</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="I68" s="5">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="J68" s="5">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5438,30 +5428,40 @@
         <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="P68" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+      <c r="Q68" s="5">
+        <v>46281</v>
+      </c>
+      <c r="R68" s="5">
+        <v>46275</v>
+      </c>
+      <c r="S68" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T68" s="6">
+        <v>0</v>
+      </c>
+      <c r="U68" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B69" s="9">
-        <v>46225.862226516205</v>
+        <v>46225.862234050925</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46232.62438219908</v>
+        <v>46225.870632060185</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>226</v>
+        <v>150</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5488,40 +5488,30 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q69" s="9">
-        <v>46281</v>
-      </c>
-      <c r="R69" s="9">
-        <v>46275</v>
-      </c>
-      <c r="S69" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T69" s="10">
-        <v>0</v>
-      </c>
-      <c r="U69" s="11" t="s">
-        <v>90</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
-        <v>46225.862234050925</v>
+        <v>46225.86224180556</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46225.870632060185</v>
+        <v>46225.87064059028</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>150</v>
@@ -5551,13 +5541,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5567,14 +5557,14 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B71" s="9">
-        <v>46225.86224180556</v>
+        <v>46225.862249224534</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46225.87064059028</v>
+        <v>46225.87065297454</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>150</v>
@@ -5604,13 +5594,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5620,14 +5610,14 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B72" s="5">
-        <v>46225.862249224534</v>
+        <v>46225.86225659722</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46225.87065297454</v>
+        <v>46225.87067319444</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>150</v>
@@ -5657,13 +5647,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5673,17 +5663,17 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B73" s="9">
-        <v>46225.86225659722</v>
+        <v>46225.862276388885</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46225.87067319444</v>
+        <v>46232.624382141206</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5695,10 +5685,10 @@
         <v>57</v>
       </c>
       <c r="I73" s="9">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="J73" s="9">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="K73" s="10" t="s">
         <v>26</v>
@@ -5710,33 +5700,43 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>150</v>
+        <v>234</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="Q73" s="10"/>
-      <c r="R73" s="10"/>
-      <c r="S73" s="10"/>
-      <c r="T73" s="10"/>
-      <c r="U73" s="10"/>
+      <c r="Q73" s="9">
+        <v>46286</v>
+      </c>
+      <c r="R73" s="9">
+        <v>46286</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T73" s="10">
+        <v>0</v>
+      </c>
+      <c r="U73" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>236</v>
       </c>
       <c r="B74" s="5">
-        <v>46225.862276388885</v>
+        <v>46225.862283842594</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46232.624382141206</v>
+        <v>46238.48726658565</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>237</v>
+        <v>150</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5747,9 +5747,7 @@
       <c r="H74" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I74" s="5">
-        <v>46286</v>
-      </c>
+      <c r="I74" s="6"/>
       <c r="J74" s="5">
         <v>46286</v>
       </c>
@@ -5763,40 +5761,30 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P74" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46286</v>
-      </c>
-      <c r="R74" s="5">
-        <v>46286</v>
-      </c>
-      <c r="S74" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="11" t="s">
-        <v>90</v>
-      </c>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B75" s="9">
-        <v>46225.862283842594</v>
+        <v>46225.86229252315</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46238.48726658565</v>
+        <v>46238.487257326386</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>150</v>
@@ -5824,13 +5812,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5840,14 +5828,14 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B76" s="5">
-        <v>46225.86229252315</v>
+        <v>46225.862306932875</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46238.487257326386</v>
+        <v>46238.48726778935</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>150</v>
@@ -5875,13 +5863,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="O76" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="O76" s="6" t="s">
-        <v>244</v>
-      </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5891,14 +5879,14 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B77" s="9">
-        <v>46225.862306932875</v>
+        <v>46225.86231524305</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46238.48726778935</v>
+        <v>46225.870728344904</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>150</v>
@@ -5926,13 +5914,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="O77" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="P77" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="P77" s="10" t="s">
-        <v>242</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5942,17 +5930,17 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B78" s="5">
-        <v>46225.86231524305</v>
+        <v>46225.862381087965</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46225.870728344904</v>
+        <v>46232.62438238426</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5963,9 +5951,11 @@
       <c r="H78" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I78" s="6"/>
+      <c r="I78" s="5">
+        <v>46287</v>
+      </c>
       <c r="J78" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
@@ -5977,33 +5967,43 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
+        <v>247</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>46287</v>
+      </c>
+      <c r="R78" s="5">
+        <v>46287</v>
+      </c>
+      <c r="S78" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T78" s="6">
+        <v>0</v>
+      </c>
+      <c r="U78" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
         <v>248</v>
       </c>
       <c r="B79" s="9">
-        <v>46225.862381087965</v>
+        <v>46225.862389155096</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46232.62438238426</v>
+        <v>46225.870759178244</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>249</v>
+        <v>150</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6030,40 +6030,30 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="P79" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q79" s="9">
-        <v>46287</v>
-      </c>
-      <c r="R79" s="9">
-        <v>46287</v>
-      </c>
-      <c r="S79" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T79" s="10">
-        <v>0</v>
-      </c>
-      <c r="U79" s="11" t="s">
-        <v>90</v>
-      </c>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
+      <c r="U79" s="10"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
-        <v>46225.862389155096</v>
+        <v>46225.86239770833</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46225.870759178244</v>
+        <v>46225.870777442135</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>150</v>
@@ -6093,13 +6083,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="O80" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="O80" s="6" t="s">
-        <v>253</v>
-      </c>
       <c r="P80" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6109,14 +6099,14 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B81" s="9">
-        <v>46225.86239770833</v>
+        <v>46225.86240878473</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46225.870777442135</v>
+        <v>46225.870787824075</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>150</v>
@@ -6146,13 +6136,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="O81" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="O81" s="10" t="s">
-        <v>253</v>
-      </c>
       <c r="P81" s="10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6162,14 +6152,14 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
-        <v>46225.86240878473</v>
+        <v>46225.86241983796</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46225.870787824075</v>
+        <v>46225.87080640046</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>150</v>
@@ -6199,13 +6189,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6215,17 +6205,17 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B83" s="9">
-        <v>46225.86241983796</v>
+        <v>46225.86244091435</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46225.87080640046</v>
+        <v>46240.82253846065</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6237,10 +6227,10 @@
         <v>57</v>
       </c>
       <c r="I83" s="9">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="J83" s="9">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
@@ -6252,33 +6242,43 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>150</v>
+        <v>257</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q83" s="10"/>
-      <c r="R83" s="10"/>
-      <c r="S83" s="10"/>
-      <c r="T83" s="10"/>
-      <c r="U83" s="10"/>
+        <v>219</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>46288</v>
+      </c>
+      <c r="R83" s="9">
+        <v>46288</v>
+      </c>
+      <c r="S83" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T83" s="10">
+        <v>0</v>
+      </c>
+      <c r="U83" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B84" s="5">
-        <v>46225.86244091435</v>
+        <v>46225.86244844907</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46232.62438216435</v>
+        <v>46238.48726703704</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>223</v>
+        <v>150</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6305,40 +6305,30 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="P84" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q84" s="5">
-        <v>46288</v>
-      </c>
-      <c r="R84" s="5">
-        <v>46288</v>
-      </c>
-      <c r="S84" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="11" t="s">
-        <v>90</v>
-      </c>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+      <c r="T84" s="6"/>
+      <c r="U84" s="6"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B85" s="9">
-        <v>46225.86244844907</v>
+        <v>46225.86245663195</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46238.48726703704</v>
+        <v>46238.48725680556</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>150</v>
@@ -6368,13 +6358,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6384,14 +6374,14 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5">
-        <v>46225.86245663195</v>
+        <v>46225.862464502316</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46238.48725680556</v>
+        <v>46225.870855393514</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>150</v>
@@ -6421,13 +6411,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>263</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6437,14 +6427,14 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B87" s="9">
-        <v>46225.862464502316</v>
+        <v>46225.86247284722</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46225.870855393514</v>
+        <v>46225.87086599537</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>150</v>
@@ -6474,13 +6464,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>267</v>
+        <v>150</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6490,17 +6480,17 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B88" s="5">
-        <v>46225.86247284722</v>
+        <v>46225.86249337963</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46225.87086599537</v>
+        <v>46240.8225384375</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>150</v>
+        <v>267</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6512,10 +6502,10 @@
         <v>57</v>
       </c>
       <c r="I88" s="5">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="J88" s="5">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
@@ -6527,33 +6517,43 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
+        <v>268</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>46289</v>
+      </c>
+      <c r="R88" s="5">
+        <v>46289</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T88" s="6">
+        <v>0</v>
+      </c>
+      <c r="U88" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B89" s="9">
-        <v>46225.86249337963</v>
+        <v>46225.862501435186</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46232.6243832176</v>
+        <v>46225.87089600695</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>224</v>
+        <v>150</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6565,10 +6565,10 @@
         <v>57</v>
       </c>
       <c r="I89" s="9">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="J89" s="9">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="K89" s="10" t="s">
         <v>26</v>
@@ -6580,40 +6580,30 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="P89" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q89" s="9">
-        <v>46289</v>
-      </c>
-      <c r="R89" s="9">
-        <v>46289</v>
-      </c>
-      <c r="S89" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T89" s="10">
-        <v>0</v>
-      </c>
-      <c r="U89" s="11" t="s">
-        <v>90</v>
-      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B90" s="5">
-        <v>46225.862501435186</v>
+        <v>46225.8625115162</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46225.87089600695</v>
+        <v>46225.87090469907</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>150</v>
@@ -6643,13 +6633,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6659,14 +6649,14 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B91" s="9">
-        <v>46225.8625115162</v>
+        <v>46225.8625234375</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46225.87090469907</v>
+        <v>46225.870913969906</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>150</v>
@@ -6696,13 +6686,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6712,14 +6702,14 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B92" s="5">
-        <v>46225.8625234375</v>
+        <v>46225.86257370371</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46225.870913969906</v>
+        <v>46225.870925243056</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>150</v>
@@ -6749,10 +6739,10 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>274</v>
+        <v>150</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>275</v>
@@ -6765,17 +6755,17 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B93" s="9">
-        <v>46225.86257370371</v>
+        <v>46225.86260116898</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46225.870925243056</v>
+        <v>46232.62438732639</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>150</v>
+        <v>268</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6787,10 +6777,10 @@
         <v>57</v>
       </c>
       <c r="I93" s="9">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="J93" s="9">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="K93" s="10" t="s">
         <v>26</v>
@@ -6802,33 +6792,43 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>150</v>
+        <v>277</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q93" s="10"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="10"/>
-      <c r="T93" s="10"/>
-      <c r="U93" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q93" s="9">
+        <v>46293</v>
+      </c>
+      <c r="R93" s="9">
+        <v>46293</v>
+      </c>
+      <c r="S93" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T93" s="10">
+        <v>0</v>
+      </c>
+      <c r="U93" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B94" s="5">
-        <v>46225.86260116898</v>
+        <v>46225.8626096875</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46232.62438732639</v>
+        <v>46225.87095484954</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>272</v>
+        <v>150</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6855,40 +6855,30 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>219</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q94" s="5">
-        <v>46293</v>
-      </c>
-      <c r="R94" s="5">
-        <v>46293</v>
-      </c>
-      <c r="S94" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T94" s="6">
-        <v>0</v>
-      </c>
-      <c r="U94" s="11" t="s">
-        <v>90</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B95" s="9">
-        <v>46225.8626096875</v>
+        <v>46225.86261736111</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46225.87095484954</v>
+        <v>46225.87096165509</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>150</v>
@@ -6918,13 +6908,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6934,14 +6924,14 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B96" s="5">
-        <v>46225.86261736111</v>
+        <v>46225.86262487269</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46225.87096165509</v>
+        <v>46225.87097416667</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>150</v>
@@ -6971,13 +6961,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6987,14 +6977,14 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B97" s="9">
-        <v>46225.86262487269</v>
+        <v>46225.862632268516</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46225.87097416667</v>
+        <v>46225.870994074074</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>150</v>
@@ -7024,13 +7014,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7040,33 +7030,27 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B98" s="5">
-        <v>46225.862632268516</v>
+        <v>46225.86265351852</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46225.870994074074</v>
+        <v>46225.86288905093</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>150</v>
+        <v>285</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I98" s="5">
-        <v>46293</v>
-      </c>
-      <c r="J98" s="5">
-        <v>46293</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
       <c r="K98" s="6" t="s">
         <v>26</v>
       </c>
@@ -7074,16 +7058,16 @@
         <v>26</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>272</v>
+        <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>150</v>
+        <v>286</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>283</v>
+        <v>26</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7093,27 +7077,33 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B99" s="9">
-        <v>46225.86265351852</v>
+        <v>46225.86265758102</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46225.86288905093</v>
+        <v>46225.86992599537</v>
       </c>
       <c r="E99" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="10"/>
-      <c r="I99" s="10"/>
-      <c r="J99" s="10"/>
+      <c r="H99" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="I99" s="9">
+        <v>46294</v>
+      </c>
+      <c r="J99" s="9">
+        <v>46294</v>
+      </c>
       <c r="K99" s="10" t="s">
         <v>26</v>
       </c>
@@ -7121,45 +7111,55 @@
         <v>26</v>
       </c>
       <c r="M99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="O99" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="P99" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q99" s="9">
+        <v>46294</v>
+      </c>
+      <c r="R99" s="9">
+        <v>46294</v>
+      </c>
+      <c r="S99" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T99" s="10">
         <v>0</v>
       </c>
-      <c r="N99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O99" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="P99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q99" s="10"/>
-      <c r="R99" s="10"/>
-      <c r="S99" s="10"/>
-      <c r="T99" s="10"/>
-      <c r="U99" s="10"/>
+      <c r="U99" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B100" s="5">
-        <v>46225.86265758102</v>
+        <v>46225.86266576389</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46225.86992599537</v>
+        <v>46225.87103081019</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>292</v>
+        <v>150</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I100" s="5">
         <v>46294</v>
@@ -7177,40 +7177,30 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q100" s="5">
-        <v>46294</v>
-      </c>
-      <c r="R100" s="5">
-        <v>46294</v>
-      </c>
-      <c r="S100" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T100" s="6">
-        <v>0</v>
-      </c>
-      <c r="U100" s="11" t="s">
-        <v>90</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6"/>
+      <c r="T100" s="6"/>
+      <c r="U100" s="6"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B101" s="9">
-        <v>46225.86266576389</v>
+        <v>46225.86267326389</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46225.87103081019</v>
+        <v>46225.87104060185</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>150</v>
@@ -7219,10 +7209,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I101" s="9">
         <v>46294</v>
@@ -7240,13 +7230,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7256,14 +7246,14 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B102" s="5">
-        <v>46225.86267326389</v>
+        <v>46225.86268015046</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46225.87104060185</v>
+        <v>46225.87104780093</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>150</v>
@@ -7272,10 +7262,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I102" s="5">
         <v>46294</v>
@@ -7293,13 +7283,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7309,14 +7299,14 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B103" s="9">
-        <v>46225.86268015046</v>
+        <v>46225.862687326386</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46225.87104780093</v>
+        <v>46225.871064861116</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>150</v>
@@ -7325,10 +7315,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I103" s="9">
         <v>46294</v>
@@ -7346,13 +7336,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7362,32 +7352,32 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B104" s="5">
-        <v>46225.862687326386</v>
+        <v>46225.86270745371</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46225.871064861116</v>
+        <v>46225.86997988426</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>150</v>
+        <v>299</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>293</v>
+        <v>56</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>294</v>
+        <v>57</v>
       </c>
       <c r="I104" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="J104" s="5">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>26</v>
@@ -7399,33 +7389,43 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="6"/>
-      <c r="S104" s="6"/>
-      <c r="T104" s="6"/>
-      <c r="U104" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q104" s="5">
+        <v>46295</v>
+      </c>
+      <c r="R104" s="5">
+        <v>46295</v>
+      </c>
+      <c r="S104" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T104" s="6">
+        <v>0</v>
+      </c>
+      <c r="U104" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B105" s="9">
-        <v>46225.86270745371</v>
+        <v>46225.8627578125</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46225.86997988426</v>
+        <v>46225.87109706018</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>303</v>
+        <v>150</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7452,40 +7452,30 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>304</v>
+        <v>150</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q105" s="9">
-        <v>46295</v>
-      </c>
-      <c r="R105" s="9">
-        <v>46295</v>
-      </c>
-      <c r="S105" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T105" s="10">
-        <v>0</v>
-      </c>
-      <c r="U105" s="11" t="s">
-        <v>90</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="Q105" s="10"/>
+      <c r="R105" s="10"/>
+      <c r="S105" s="10"/>
+      <c r="T105" s="10"/>
+      <c r="U105" s="10"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B106" s="5">
-        <v>46225.8627578125</v>
+        <v>46225.86276570601</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46225.87109706018</v>
+        <v>46225.871105266204</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>150</v>
@@ -7515,13 +7505,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7531,14 +7521,14 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B107" s="9">
-        <v>46225.86276570601</v>
+        <v>46225.86277225694</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46225.871105266204</v>
+        <v>46225.87111719907</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>150</v>
@@ -7568,13 +7558,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7584,14 +7574,14 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B108" s="5">
-        <v>46225.86277225694</v>
+        <v>46225.86277868056</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46225.87111719907</v>
+        <v>46225.8711331713</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>150</v>
@@ -7621,13 +7611,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7637,32 +7627,32 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B109" s="9">
-        <v>46225.86277868056</v>
+        <v>46225.8627980787</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46225.8711331713</v>
+        <v>46225.870042650466</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>150</v>
+        <v>307</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="I109" s="9">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="J109" s="9">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K109" s="10" t="s">
         <v>26</v>
@@ -7674,33 +7664,43 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q109" s="10"/>
-      <c r="R109" s="10"/>
-      <c r="S109" s="10"/>
-      <c r="T109" s="10"/>
-      <c r="U109" s="10"/>
+        <v>285</v>
+      </c>
+      <c r="Q109" s="9">
+        <v>46296</v>
+      </c>
+      <c r="R109" s="9">
+        <v>46296</v>
+      </c>
+      <c r="S109" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T109" s="10">
+        <v>0</v>
+      </c>
+      <c r="U109" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B110" s="5">
-        <v>46225.8627980787</v>
+        <v>46225.86280646991</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46225.870042650466</v>
+        <v>46225.87116359954</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>311</v>
+        <v>150</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7727,40 +7727,30 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q110" s="5">
-        <v>46296</v>
-      </c>
-      <c r="R110" s="5">
-        <v>46296</v>
-      </c>
-      <c r="S110" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T110" s="6">
-        <v>0</v>
-      </c>
-      <c r="U110" s="11" t="s">
-        <v>90</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+      <c r="U110" s="6"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B111" s="9">
-        <v>46225.86280646991</v>
+        <v>46225.8628134375</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46225.87116359954</v>
+        <v>46225.87117237269</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>150</v>
@@ -7790,13 +7780,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="O111" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="P111" s="10" t="s">
         <v>311</v>
-      </c>
-      <c r="O111" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>313</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7806,14 +7796,14 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B112" s="5">
-        <v>46225.8628134375</v>
+        <v>46225.86282005787</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46225.87117237269</v>
+        <v>46225.8711906713</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>150</v>
@@ -7843,13 +7833,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="O112" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="P112" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="O112" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>315</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7859,14 +7849,14 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B113" s="9">
-        <v>46225.86282005787</v>
+        <v>46225.862826516204</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46225.8711906713</v>
+        <v>46225.87120541667</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>150</v>
@@ -7896,13 +7886,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="O113" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="P113" s="10" t="s">
         <v>311</v>
-      </c>
-      <c r="O113" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="P113" s="10" t="s">
-        <v>315</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7912,17 +7902,17 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B114" s="5">
-        <v>46225.862826516204</v>
+        <v>46225.86284444445</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46225.87120541667</v>
+        <v>46225.87010216435</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>150</v>
+        <v>315</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7934,10 +7924,10 @@
         <v>184</v>
       </c>
       <c r="I114" s="5">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="J114" s="5">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>26</v>
@@ -7949,33 +7939,43 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="6"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
+        <v>316</v>
+      </c>
+      <c r="Q114" s="5">
+        <v>46297</v>
+      </c>
+      <c r="R114" s="5">
+        <v>46297</v>
+      </c>
+      <c r="S114" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T114" s="6">
+        <v>0</v>
+      </c>
+      <c r="U114" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B115" s="9">
-        <v>46225.86284444445</v>
+        <v>46225.86285697916</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46225.87010216435</v>
+        <v>46225.87123498843</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>319</v>
+        <v>150</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8002,40 +8002,30 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q115" s="9">
-        <v>46297</v>
-      </c>
-      <c r="R115" s="9">
-        <v>46297</v>
-      </c>
-      <c r="S115" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T115" s="10">
-        <v>0</v>
-      </c>
-      <c r="U115" s="11" t="s">
-        <v>90</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="Q115" s="10"/>
+      <c r="R115" s="10"/>
+      <c r="S115" s="10"/>
+      <c r="T115" s="10"/>
+      <c r="U115" s="10"/>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B116" s="5">
-        <v>46225.86285697916</v>
+        <v>46225.862862939815</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46225.87123498843</v>
+        <v>46225.87124284722</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>150</v>
@@ -8065,13 +8055,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8081,14 +8071,14 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B117" s="9">
-        <v>46225.862862939815</v>
+        <v>46225.86286878472</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46225.87124284722</v>
+        <v>46225.87125150463</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>150</v>
@@ -8118,13 +8108,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>150</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8134,14 +8124,14 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B118" s="5">
-        <v>46225.86286878472</v>
+        <v>46225.86287459491</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46225.87125150463</v>
+        <v>46225.87127599537</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>150</v>
@@ -8171,13 +8161,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>150</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8187,33 +8177,27 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B119" s="9">
-        <v>46225.86287459491</v>
+        <v>46225.862925532405</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46225.87127599537</v>
+        <v>46225.86295643519</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>150</v>
+        <v>324</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I119" s="9">
-        <v>46297</v>
-      </c>
-      <c r="J119" s="9">
-        <v>46297</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="10"/>
+      <c r="I119" s="10"/>
+      <c r="J119" s="10"/>
       <c r="K119" s="10" t="s">
         <v>26</v>
       </c>
@@ -8221,16 +8205,16 @@
         <v>26</v>
       </c>
       <c r="M119" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>319</v>
+        <v>26</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>319</v>
+        <v>26</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8240,27 +8224,33 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B120" s="5">
-        <v>46225.862925532405</v>
+        <v>46225.862929201394</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46225.86295643519</v>
+        <v>46225.86295732639</v>
       </c>
       <c r="E120" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G120" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="F120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
+      <c r="H120" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="I120" s="5">
+        <v>46300</v>
+      </c>
+      <c r="J120" s="5">
+        <v>46304</v>
+      </c>
       <c r="K120" s="6" t="s">
         <v>26</v>
       </c>
@@ -8268,45 +8258,55 @@
         <v>26</v>
       </c>
       <c r="M120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N120" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="O120" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="P120" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q120" s="5">
+        <v>46304</v>
+      </c>
+      <c r="R120" s="5">
+        <v>46300</v>
+      </c>
+      <c r="S120" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="T120" s="6">
         <v>0</v>
       </c>
-      <c r="N120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O120" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="P120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q120" s="6"/>
-      <c r="R120" s="6"/>
-      <c r="S120" s="6"/>
-      <c r="T120" s="6"/>
-      <c r="U120" s="6"/>
+      <c r="U120" s="11" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B121" s="9">
-        <v>46225.862929201394</v>
+        <v>46225.86294039352</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46225.86295732639</v>
+        <v>46225.86295819444</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>332</v>
+        <v>30</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>333</v>
+        <v>31</v>
       </c>
       <c r="I121" s="9">
         <v>46300</v>
@@ -8324,13 +8324,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="Q121" s="9">
         <v>46304</v>
@@ -8345,69 +8345,6 @@
         <v>0</v>
       </c>
       <c r="U121" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="B122" s="5">
-        <v>46225.86294039352</v>
-      </c>
-      <c r="C122" s="6"/>
-      <c r="D122" s="5">
-        <v>46225.86295819444</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I122" s="5">
-        <v>46300</v>
-      </c>
-      <c r="J122" s="5">
-        <v>46304</v>
-      </c>
-      <c r="K122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N122" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="O122" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q122" s="5">
-        <v>46304</v>
-      </c>
-      <c r="R122" s="5">
-        <v>46300</v>
-      </c>
-      <c r="S122" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="T122" s="6">
-        <v>0</v>
-      </c>
-      <c r="U122" s="11" t="s">
         <v>90</v>
       </c>
     </row>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -3634,7 +3634,7 @@
         <v>46238.48719537037</v>
       </c>
       <c r="D37" s="9">
-        <v>46238.48721753473</v>
+        <v>46242.20040111111</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>138</v>
@@ -3678,8 +3678,8 @@
       <c r="R37" s="9">
         <v>46237</v>
       </c>
-      <c r="S37" s="12" t="s">
-        <v>72</v>
+      <c r="S37" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T37" s="10">
         <v>1</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -3699,7 +3699,7 @@
         <v>46238.487247916666</v>
       </c>
       <c r="D38" s="5">
-        <v>46238.48726421296</v>
+        <v>46245.191039247686</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>70</v>
@@ -3743,8 +3743,8 @@
       <c r="R38" s="5">
         <v>46244</v>
       </c>
-      <c r="S38" s="12" t="s">
-        <v>72</v>
+      <c r="S38" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -2480,7 +2480,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46239.186343124995</v>
+        <v>46246.17040084491</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>68</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46239.186343124995</v>
+        <v>46246.170403310185</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46239.18634349537</v>
+        <v>46246.170404687495</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>78</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46239.18634339121</v>
+        <v>46246.170405937504</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="333">
   <si>
     <t>50001582 - "XEMORTIZ LA CANTERA"</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t>Generación OC corte laser   OT 4381 ,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>Tarea en curso</t>
@@ -2480,7 +2477,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46246.17040084491</v>
+        <v>46247.18257321759</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>68</v>
@@ -2524,29 +2521,29 @@
       <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>72</v>
+      <c r="S17" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" s="5">
         <v>46225.86165034722</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46246.170403310185</v>
+        <v>46247.182573275466</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2579,7 +2576,7 @@
         <v>70</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q18" s="5">
         <v>46246</v>
@@ -2587,29 +2584,29 @@
       <c r="R18" s="5">
         <v>46245</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>72</v>
+      <c r="S18" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19" s="9">
         <v>46225.86165694444</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46246.170404687495</v>
+        <v>46247.18257318287</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2642,7 +2639,7 @@
         <v>70</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q19" s="9">
         <v>46246</v>
@@ -2650,29 +2647,29 @@
       <c r="R19" s="9">
         <v>46245</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>72</v>
+      <c r="S19" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" s="5">
         <v>46225.86166292824</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46246.170405937504</v>
+        <v>46247.182573252314</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2705,7 +2702,7 @@
         <v>70</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q20" s="5">
         <v>46246</v>
@@ -2713,19 +2710,19 @@
       <c r="R20" s="5">
         <v>46245</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>72</v>
+      <c r="S20" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" s="9">
         <v>46225.861460914355</v>
@@ -2735,7 +2732,7 @@
         <v>46225.86191712963</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2759,7 +2756,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2772,7 +2769,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5">
         <v>46225.86167002315</v>
@@ -2782,16 +2779,16 @@
         <v>46225.8660337037</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="I22" s="5">
         <v>46247</v>
@@ -2809,13 +2806,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q22" s="5">
         <v>46259</v>
@@ -2830,12 +2827,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="9">
         <v>46225.86167825232</v>
@@ -2845,16 +2842,16 @@
         <v>46225.86694637731</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="I23" s="9">
         <v>46247</v>
@@ -2872,13 +2869,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>68</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2889,12 +2886,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46225.86168543981</v>
@@ -2904,16 +2901,16 @@
         <v>46225.867042893515</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="I24" s="5">
         <v>46251</v>
@@ -2931,13 +2928,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2948,12 +2945,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="9">
         <v>46225.86169273148</v>
@@ -2963,16 +2960,16 @@
         <v>46225.86610908565</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="I25" s="9">
         <v>46247</v>
@@ -2990,10 +2987,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3011,12 +3008,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46225.86169921297</v>
@@ -3026,16 +3023,16 @@
         <v>46225.86712378472</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="I26" s="5">
         <v>46247</v>
@@ -3053,13 +3050,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3069,7 +3066,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B27" s="9">
         <v>46225.86170601852</v>
@@ -3079,16 +3076,16 @@
         <v>46225.8671391088</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="I27" s="9">
         <v>46251</v>
@@ -3106,13 +3103,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3122,7 +3119,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46225.86175964121</v>
@@ -3132,16 +3129,16 @@
         <v>46225.86617241898</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3159,10 +3156,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3180,12 +3177,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="9">
         <v>46225.861767326394</v>
@@ -3195,16 +3192,16 @@
         <v>46225.86719211805</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="I29" s="9">
         <v>46247</v>
@@ -3222,13 +3219,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3238,7 +3235,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46225.8617740162</v>
@@ -3248,16 +3245,16 @@
         <v>46225.86721106482</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="I30" s="5">
         <v>46251</v>
@@ -3275,13 +3272,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3291,7 +3288,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="9">
         <v>46225.86178056713</v>
@@ -3301,16 +3298,16 @@
         <v>46225.866204108796</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3328,10 +3325,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3349,12 +3346,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46225.8617949537</v>
@@ -3364,16 +3361,16 @@
         <v>46237.553715648144</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3391,13 +3388,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3407,7 +3404,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B33" s="9">
         <v>46225.86180262732</v>
@@ -3417,16 +3414,16 @@
         <v>46225.86759815972</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3444,13 +3441,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3460,7 +3457,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46225.8618097338</v>
@@ -3470,16 +3467,16 @@
         <v>46225.867627534724</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3497,13 +3494,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3513,7 +3510,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B35" s="9">
         <v>46225.86181672454</v>
@@ -3523,7 +3520,7 @@
         <v>46238.48726621528</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3547,7 +3544,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3560,7 +3557,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46225.86182068287</v>
@@ -3572,16 +3569,16 @@
         <v>46235.207714502314</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3599,13 +3596,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>47</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3625,7 +3622,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B37" s="9">
         <v>46225.86182918982</v>
@@ -3637,16 +3634,16 @@
         <v>46242.20040111111</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3664,13 +3661,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3690,7 +3687,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46225.86183666666</v>
@@ -3708,10 +3705,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3729,13 +3726,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3755,7 +3752,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="9">
         <v>46225.86185291667</v>
@@ -3765,16 +3762,16 @@
         <v>46225.869796087965</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3792,13 +3789,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3813,12 +3810,12 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46225.86186070602</v>
@@ -3828,16 +3825,16 @@
         <v>46225.870297002315</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3853,13 +3850,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="P40" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3869,7 +3866,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="9">
         <v>46225.861866770836</v>
@@ -3879,16 +3876,16 @@
         <v>46225.870431400464</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3904,13 +3901,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3920,7 +3917,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46225.861897951385</v>
@@ -3930,16 +3927,16 @@
         <v>46225.87044054398</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -3955,13 +3952,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3971,7 +3968,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46225.86190395833</v>
@@ -3981,16 +3978,16 @@
         <v>46225.87046690972</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -4006,13 +4003,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4022,7 +4019,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46225.86196252315</v>
@@ -4032,7 +4029,7 @@
         <v>46225.86211475694</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>25</v>
@@ -4056,7 +4053,7 @@
         <v>26</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4069,7 +4066,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="9">
         <v>46225.86196658565</v>
@@ -4079,16 +4076,16 @@
         <v>46225.866340925924</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="9">
@@ -4104,13 +4101,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -4125,12 +4122,12 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46225.86197478009</v>
@@ -4140,16 +4137,16 @@
         <v>46225.8663590625</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I46" s="5">
         <v>46260</v>
@@ -4167,13 +4164,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q46" s="5">
         <v>46260</v>
@@ -4188,12 +4185,12 @@
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="9">
         <v>46225.86198239583</v>
@@ -4203,16 +4200,16 @@
         <v>46225.86637913194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I47" s="9">
         <v>46260</v>
@@ -4230,13 +4227,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="9">
         <v>46260</v>
@@ -4251,12 +4248,12 @@
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46225.86198986111</v>
@@ -4266,16 +4263,16 @@
         <v>46225.866400115745</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4293,13 +4290,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4314,12 +4311,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" s="9">
         <v>46225.86199775463</v>
@@ -4329,16 +4326,16 @@
         <v>46225.86644668982</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="I49" s="9">
         <v>46261</v>
@@ -4356,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q49" s="9">
         <v>46261</v>
@@ -4377,12 +4374,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46225.86200543982</v>
@@ -4392,16 +4389,16 @@
         <v>46225.86650415509</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4419,13 +4416,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="5">
         <v>46261</v>
@@ -4440,12 +4437,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B51" s="9">
         <v>46225.86201293982</v>
@@ -4455,7 +4452,7 @@
         <v>46225.862125590276</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>25</v>
@@ -4479,7 +4476,7 @@
         <v>26</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4492,7 +4489,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46225.86201641204</v>
@@ -4502,16 +4499,16 @@
         <v>46225.867920069446</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46262</v>
@@ -4529,13 +4526,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q52" s="5">
         <v>46266</v>
@@ -4550,12 +4547,12 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="9">
         <v>46225.86202538194</v>
@@ -4565,16 +4562,16 @@
         <v>46225.86836851852</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4592,13 +4589,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q53" s="9">
         <v>46273</v>
@@ -4613,12 +4610,12 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46225.86203225695</v>
@@ -4628,16 +4625,16 @@
         <v>46238.487257870365</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46267</v>
@@ -4655,13 +4652,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4671,7 +4668,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B55" s="9">
         <v>46225.86204296297</v>
@@ -4681,16 +4678,16 @@
         <v>46238.48725839121</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I55" s="9">
         <v>46267</v>
@@ -4708,13 +4705,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4724,7 +4721,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46225.862053379635</v>
@@ -4734,16 +4731,16 @@
         <v>46238.48725583333</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I56" s="5">
         <v>46267</v>
@@ -4761,13 +4758,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4777,7 +4774,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B57" s="9">
         <v>46225.86206356481</v>
@@ -4787,16 +4784,16 @@
         <v>46225.870545729165</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I57" s="9">
         <v>46267</v>
@@ -4814,13 +4811,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4830,7 +4827,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B58" s="5">
         <v>46225.86208298611</v>
@@ -4840,16 +4837,16 @@
         <v>46225.86841018518</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -4867,13 +4864,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q58" s="5">
         <v>46274</v>
@@ -4888,12 +4885,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B59" s="9">
         <v>46225.862089999995</v>
@@ -4903,16 +4900,16 @@
         <v>46238.487258877314</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="I59" s="9">
         <v>46274</v>
@@ -4930,13 +4927,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>201</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4946,7 +4943,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46225.86209783565</v>
@@ -4956,16 +4953,16 @@
         <v>46238.48726738426</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I60" s="5">
         <v>46274</v>
@@ -4983,13 +4980,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4999,7 +4996,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B61" s="9">
         <v>46225.86210570602</v>
@@ -5009,16 +5006,16 @@
         <v>46238.48725643518</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="I61" s="9">
         <v>46274</v>
@@ -5036,13 +5033,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5052,7 +5049,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46225.86216362269</v>
@@ -5062,16 +5059,16 @@
         <v>46225.870609791666</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5089,13 +5086,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5105,7 +5102,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B63" s="9">
         <v>46225.86219280092</v>
@@ -5115,7 +5112,7 @@
         <v>46225.86232971065</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -5139,7 +5136,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5152,7 +5149,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B64" s="5">
         <v>46225.86219668981</v>
@@ -5162,16 +5159,16 @@
         <v>46232.19127755787</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I64" s="5">
         <v>46230</v>
@@ -5189,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q64" s="5">
         <v>46231</v>
@@ -5210,12 +5207,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B65" s="9">
         <v>46225.86220582176</v>
@@ -5225,16 +5222,16 @@
         <v>46232.19127729167</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I65" s="9">
         <v>46230</v>
@@ -5252,13 +5249,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="9">
         <v>46231</v>
@@ -5273,12 +5270,12 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5">
         <v>46225.86221482639</v>
@@ -5288,16 +5285,16 @@
         <v>46232.19127710648</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5315,13 +5312,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5336,12 +5333,12 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B67" s="9">
         <v>46225.862222800926</v>
@@ -5351,7 +5348,7 @@
         <v>46232.60338638889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>25</v>
@@ -5375,7 +5372,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>26</v>
@@ -5388,7 +5385,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B68" s="5">
         <v>46225.862226516205</v>
@@ -5398,7 +5395,7 @@
         <v>46232.62438219908</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5425,13 +5422,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46281</v>
@@ -5446,12 +5443,12 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B69" s="9">
         <v>46225.862234050925</v>
@@ -5461,7 +5458,7 @@
         <v>46225.870632060185</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5488,13 +5485,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5504,7 +5501,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B70" s="5">
         <v>46225.86224180556</v>
@@ -5514,7 +5511,7 @@
         <v>46225.87064059028</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5541,13 +5538,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5557,7 +5554,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B71" s="9">
         <v>46225.862249224534</v>
@@ -5567,7 +5564,7 @@
         <v>46225.87065297454</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5594,13 +5591,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5610,7 +5607,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B72" s="5">
         <v>46225.86225659722</v>
@@ -5620,7 +5617,7 @@
         <v>46225.87067319444</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5647,13 +5644,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5663,7 +5660,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B73" s="9">
         <v>46225.862276388885</v>
@@ -5673,7 +5670,7 @@
         <v>46232.624382141206</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5700,13 +5697,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="Q73" s="9">
         <v>46286</v>
@@ -5721,12 +5718,12 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B74" s="5">
         <v>46225.862283842594</v>
@@ -5736,7 +5733,7 @@
         <v>46238.48726658565</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5761,13 +5758,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5777,7 +5774,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B75" s="9">
         <v>46225.86229252315</v>
@@ -5787,7 +5784,7 @@
         <v>46238.487257326386</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5812,13 +5809,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5828,7 +5825,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B76" s="5">
         <v>46225.862306932875</v>
@@ -5838,7 +5835,7 @@
         <v>46238.48726778935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5863,13 +5860,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5879,7 +5876,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B77" s="9">
         <v>46225.86231524305</v>
@@ -5889,7 +5886,7 @@
         <v>46225.870728344904</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5914,13 +5911,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5930,7 +5927,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B78" s="5">
         <v>46225.862381087965</v>
@@ -5940,7 +5937,7 @@
         <v>46232.62438238426</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5967,13 +5964,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>247</v>
       </c>
       <c r="Q78" s="5">
         <v>46287</v>
@@ -5988,12 +5985,12 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B79" s="9">
         <v>46225.862389155096</v>
@@ -6003,7 +6000,7 @@
         <v>46225.870759178244</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6030,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6046,7 +6043,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B80" s="5">
         <v>46225.86239770833</v>
@@ -6056,7 +6053,7 @@
         <v>46225.870777442135</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6083,13 +6080,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6099,7 +6096,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B81" s="9">
         <v>46225.86240878473</v>
@@ -6109,7 +6106,7 @@
         <v>46225.870787824075</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6136,13 +6133,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6152,7 +6149,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B82" s="5">
         <v>46225.86241983796</v>
@@ -6162,7 +6159,7 @@
         <v>46225.87080640046</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6189,13 +6186,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6205,7 +6202,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B83" s="9">
         <v>46225.86244091435</v>
@@ -6215,7 +6212,7 @@
         <v>46240.82253846065</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6242,13 +6239,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q83" s="9">
         <v>46288</v>
@@ -6263,12 +6260,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B84" s="5">
         <v>46225.86244844907</v>
@@ -6278,7 +6275,7 @@
         <v>46238.48726703704</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6305,13 +6302,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>259</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6321,7 +6318,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B85" s="9">
         <v>46225.86245663195</v>
@@ -6331,7 +6328,7 @@
         <v>46238.48725680556</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6358,13 +6355,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O85" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="P85" s="10" t="s">
         <v>259</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>260</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6374,7 +6371,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B86" s="5">
         <v>46225.862464502316</v>
@@ -6384,7 +6381,7 @@
         <v>46225.870855393514</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6411,13 +6408,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6427,7 +6424,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B87" s="9">
         <v>46225.86247284722</v>
@@ -6437,7 +6434,7 @@
         <v>46225.87086599537</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6464,13 +6461,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6480,7 +6477,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B88" s="5">
         <v>46225.86249337963</v>
@@ -6490,7 +6487,7 @@
         <v>46240.8225384375</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6517,13 +6514,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q88" s="5">
         <v>46289</v>
@@ -6538,12 +6535,12 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B89" s="9">
         <v>46225.862501435186</v>
@@ -6553,7 +6550,7 @@
         <v>46225.87089600695</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6580,13 +6577,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6596,7 +6593,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B90" s="5">
         <v>46225.8625115162</v>
@@ -6606,7 +6603,7 @@
         <v>46225.87090469907</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6633,13 +6630,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>270</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>271</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6649,7 +6646,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B91" s="9">
         <v>46225.8625234375</v>
@@ -6659,7 +6656,7 @@
         <v>46225.870913969906</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6686,13 +6683,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6702,7 +6699,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B92" s="5">
         <v>46225.86257370371</v>
@@ -6712,7 +6709,7 @@
         <v>46225.870925243056</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6739,13 +6736,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6755,7 +6752,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B93" s="9">
         <v>46225.86260116898</v>
@@ -6765,7 +6762,7 @@
         <v>46232.62438732639</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6792,10 +6789,10 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6813,12 +6810,12 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B94" s="5">
         <v>46225.8626096875</v>
@@ -6828,7 +6825,7 @@
         <v>46225.87095484954</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6855,13 +6852,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6871,7 +6868,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B95" s="9">
         <v>46225.86261736111</v>
@@ -6881,7 +6878,7 @@
         <v>46225.87096165509</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6908,13 +6905,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6924,7 +6921,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B96" s="5">
         <v>46225.86262487269</v>
@@ -6934,7 +6931,7 @@
         <v>46225.87097416667</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6961,13 +6958,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6977,7 +6974,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B97" s="9">
         <v>46225.862632268516</v>
@@ -6987,7 +6984,7 @@
         <v>46225.870994074074</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7014,13 +7011,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7030,7 +7027,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B98" s="5">
         <v>46225.86265351852</v>
@@ -7040,7 +7037,7 @@
         <v>46225.86288905093</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7064,7 +7061,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7077,7 +7074,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B99" s="9">
         <v>46225.86265758102</v>
@@ -7087,16 +7084,16 @@
         <v>46225.86992599537</v>
       </c>
       <c r="E99" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="10" t="s">
+      <c r="H99" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="I99" s="9">
         <v>46294</v>
@@ -7114,13 +7111,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q99" s="9">
         <v>46294</v>
@@ -7135,12 +7132,12 @@
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B100" s="5">
         <v>46225.86266576389</v>
@@ -7150,16 +7147,16 @@
         <v>46225.87103081019</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="I100" s="5">
         <v>46294</v>
@@ -7177,13 +7174,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7193,7 +7190,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B101" s="9">
         <v>46225.86267326389</v>
@@ -7203,16 +7200,16 @@
         <v>46225.87104060185</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="I101" s="9">
         <v>46294</v>
@@ -7230,13 +7227,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7246,7 +7243,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B102" s="5">
         <v>46225.86268015046</v>
@@ -7256,16 +7253,16 @@
         <v>46225.87104780093</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="I102" s="5">
         <v>46294</v>
@@ -7283,13 +7280,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7299,7 +7296,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B103" s="9">
         <v>46225.862687326386</v>
@@ -7309,16 +7306,16 @@
         <v>46225.871064861116</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="I103" s="9">
         <v>46294</v>
@@ -7336,13 +7333,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7352,7 +7349,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B104" s="5">
         <v>46225.86270745371</v>
@@ -7362,7 +7359,7 @@
         <v>46225.86997988426</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7389,10 +7386,10 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>26</v>
@@ -7410,12 +7407,12 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B105" s="9">
         <v>46225.8627578125</v>
@@ -7425,7 +7422,7 @@
         <v>46225.87109706018</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7452,13 +7449,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7468,7 +7465,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B106" s="5">
         <v>46225.86276570601</v>
@@ -7478,7 +7475,7 @@
         <v>46225.871105266204</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7505,13 +7502,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7521,7 +7518,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B107" s="9">
         <v>46225.86277225694</v>
@@ -7531,7 +7528,7 @@
         <v>46225.87111719907</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7558,13 +7555,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7574,7 +7571,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B108" s="5">
         <v>46225.86277868056</v>
@@ -7584,7 +7581,7 @@
         <v>46225.8711331713</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7611,13 +7608,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7627,7 +7624,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B109" s="9">
         <v>46225.8627980787</v>
@@ -7637,16 +7634,16 @@
         <v>46225.870042650466</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I109" s="9">
         <v>46296</v>
@@ -7664,13 +7661,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q109" s="9">
         <v>46296</v>
@@ -7685,12 +7682,12 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B110" s="5">
         <v>46225.86280646991</v>
@@ -7700,16 +7697,16 @@
         <v>46225.87116359954</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I110" s="5">
         <v>46296</v>
@@ -7727,13 +7724,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7743,7 +7740,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B111" s="9">
         <v>46225.8628134375</v>
@@ -7753,16 +7750,16 @@
         <v>46225.87117237269</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I111" s="9">
         <v>46296</v>
@@ -7780,13 +7777,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7796,7 +7793,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B112" s="5">
         <v>46225.86282005787</v>
@@ -7806,16 +7803,16 @@
         <v>46225.8711906713</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I112" s="5">
         <v>46296</v>
@@ -7833,13 +7830,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7849,7 +7846,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B113" s="9">
         <v>46225.862826516204</v>
@@ -7859,16 +7856,16 @@
         <v>46225.87120541667</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I113" s="9">
         <v>46296</v>
@@ -7886,13 +7883,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7902,7 +7899,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B114" s="5">
         <v>46225.86284444445</v>
@@ -7912,16 +7909,16 @@
         <v>46225.87010216435</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I114" s="5">
         <v>46297</v>
@@ -7939,13 +7936,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q114" s="5">
         <v>46297</v>
@@ -7960,12 +7957,12 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B115" s="9">
         <v>46225.86285697916</v>
@@ -7975,16 +7972,16 @@
         <v>46225.87123498843</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I115" s="9">
         <v>46297</v>
@@ -8002,13 +7999,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8018,7 +8015,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B116" s="5">
         <v>46225.862862939815</v>
@@ -8028,16 +8025,16 @@
         <v>46225.87124284722</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I116" s="5">
         <v>46297</v>
@@ -8055,13 +8052,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8071,7 +8068,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B117" s="9">
         <v>46225.86286878472</v>
@@ -8081,16 +8078,16 @@
         <v>46225.87125150463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I117" s="9">
         <v>46297</v>
@@ -8108,13 +8105,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8124,7 +8121,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B118" s="5">
         <v>46225.86287459491</v>
@@ -8134,16 +8131,16 @@
         <v>46225.87127599537</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I118" s="5">
         <v>46297</v>
@@ -8161,13 +8158,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8177,7 +8174,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B119" s="9">
         <v>46225.862925532405</v>
@@ -8187,7 +8184,7 @@
         <v>46225.86295643519</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>25</v>
@@ -8211,7 +8208,7 @@
         <v>26</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>26</v>
@@ -8224,7 +8221,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B120" s="5">
         <v>46225.862929201394</v>
@@ -8234,16 +8231,16 @@
         <v>46225.86295732639</v>
       </c>
       <c r="E120" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G120" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G120" s="6" t="s">
+      <c r="H120" s="6" t="s">
         <v>328</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>329</v>
       </c>
       <c r="I120" s="5">
         <v>46300</v>
@@ -8261,13 +8258,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q120" s="5">
         <v>46304</v>
@@ -8282,12 +8279,12 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B121" s="9">
         <v>46225.86294039352</v>
@@ -8297,7 +8294,7 @@
         <v>46225.86295819444</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8324,13 +8321,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q121" s="9">
         <v>46304</v>
@@ -8345,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="U121" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46225.86694637731</v>
+        <v>46248.171457476856</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>91</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46225.86712378472</v>
+        <v>46248.17145886574</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>75</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46225.86719211805</v>
+        <v>46248.17146005787</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>81</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="334">
   <si>
     <t>50001582 - "XEMORTIZ LA CANTERA"</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC corte laser   OT 4381 ,Fabricacion corte laser  OT 4381 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -2776,7 +2779,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46225.8660337037</v>
+        <v>46252.17149778936</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -2820,19 +2823,19 @@
       <c r="R22" s="5">
         <v>46247</v>
       </c>
-      <c r="S22" s="7" t="s">
-        <v>32</v>
+      <c r="S22" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="9">
         <v>46225.86167825232</v>
@@ -2842,7 +2845,7 @@
         <v>46248.171457476856</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2875,7 +2878,7 @@
         <v>68</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2886,12 +2889,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46225.86168543981</v>
@@ -2901,7 +2904,7 @@
         <v>46225.867042893515</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2931,10 +2934,10 @@
         <v>84</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2945,22 +2948,22 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="9">
         <v>46225.86169273148</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46225.86610908565</v>
+        <v>46252.171497881944</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -2990,7 +2993,7 @@
         <v>83</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3001,19 +3004,19 @@
       <c r="R25" s="9">
         <v>46247</v>
       </c>
-      <c r="S25" s="7" t="s">
-        <v>32</v>
+      <c r="S25" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46225.86169921297</v>
@@ -3050,13 +3053,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3066,7 +3069,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B27" s="9">
         <v>46225.86170601852</v>
@@ -3076,7 +3079,7 @@
         <v>46225.8671391088</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3103,13 +3106,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3119,17 +3122,17 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" s="5">
         <v>46225.86175964121</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46225.86617241898</v>
+        <v>46252.17149795139</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3159,7 +3162,7 @@
         <v>83</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3170,19 +3173,19 @@
       <c r="R28" s="5">
         <v>46247</v>
       </c>
-      <c r="S28" s="7" t="s">
-        <v>32</v>
+      <c r="S28" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" s="9">
         <v>46225.861767326394</v>
@@ -3219,13 +3222,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>80</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3235,7 +3238,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5">
         <v>46225.8617740162</v>
@@ -3245,7 +3248,7 @@
         <v>46225.86721106482</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3272,13 +3275,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3288,7 +3291,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="9">
         <v>46225.86178056713</v>
@@ -3298,16 +3301,16 @@
         <v>46225.866204108796</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3328,7 +3331,7 @@
         <v>83</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3346,12 +3349,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46225.8617949537</v>
@@ -3361,16 +3364,16 @@
         <v>46237.553715648144</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3388,13 +3391,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3404,7 +3407,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B33" s="9">
         <v>46225.86180262732</v>
@@ -3414,16 +3417,16 @@
         <v>46225.86759815972</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3441,13 +3444,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3457,7 +3460,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46225.8618097338</v>
@@ -3467,16 +3470,16 @@
         <v>46225.867627534724</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3494,13 +3497,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3510,7 +3513,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="9">
         <v>46225.86181672454</v>
@@ -3520,7 +3523,7 @@
         <v>46238.48726621528</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3544,7 +3547,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3557,7 +3560,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46225.86182068287</v>
@@ -3569,16 +3572,16 @@
         <v>46235.207714502314</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3596,13 +3599,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>47</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3622,7 +3625,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="9">
         <v>46225.86182918982</v>
@@ -3634,16 +3637,16 @@
         <v>46242.20040111111</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3661,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3687,7 +3690,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46225.86183666666</v>
@@ -3705,10 +3708,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3726,13 +3729,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3752,7 +3755,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
         <v>46225.86185291667</v>
@@ -3762,16 +3765,16 @@
         <v>46225.869796087965</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3789,13 +3792,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3810,12 +3813,12 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46225.86186070602</v>
@@ -3825,16 +3828,16 @@
         <v>46225.870297002315</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3850,13 +3853,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3866,7 +3869,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46225.861866770836</v>
@@ -3876,16 +3879,16 @@
         <v>46225.870431400464</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3901,13 +3904,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3917,7 +3920,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46225.861897951385</v>
@@ -3927,16 +3930,16 @@
         <v>46225.87044054398</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -3952,13 +3955,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3968,7 +3971,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B43" s="9">
         <v>46225.86190395833</v>
@@ -3978,16 +3981,16 @@
         <v>46225.87046690972</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -4003,13 +4006,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4019,7 +4022,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46225.86196252315</v>
@@ -4029,7 +4032,7 @@
         <v>46225.86211475694</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>25</v>
@@ -4053,7 +4056,7 @@
         <v>26</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4066,7 +4069,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="9">
         <v>46225.86196658565</v>
@@ -4076,16 +4079,16 @@
         <v>46225.866340925924</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="9">
@@ -4101,13 +4104,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -4122,12 +4125,12 @@
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46225.86197478009</v>
@@ -4137,16 +4140,16 @@
         <v>46225.8663590625</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I46" s="5">
         <v>46260</v>
@@ -4164,13 +4167,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="5">
         <v>46260</v>
@@ -4185,12 +4188,12 @@
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="9">
         <v>46225.86198239583</v>
@@ -4200,16 +4203,16 @@
         <v>46225.86637913194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I47" s="9">
         <v>46260</v>
@@ -4227,13 +4230,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="9">
         <v>46260</v>
@@ -4248,12 +4251,12 @@
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46225.86198986111</v>
@@ -4263,16 +4266,16 @@
         <v>46225.866400115745</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4290,13 +4293,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4311,12 +4314,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" s="9">
         <v>46225.86199775463</v>
@@ -4326,16 +4329,16 @@
         <v>46225.86644668982</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I49" s="9">
         <v>46261</v>
@@ -4353,13 +4356,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q49" s="9">
         <v>46261</v>
@@ -4374,12 +4377,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46225.86200543982</v>
@@ -4389,16 +4392,16 @@
         <v>46225.86650415509</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4416,13 +4419,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="5">
         <v>46261</v>
@@ -4437,12 +4440,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="9">
         <v>46225.86201293982</v>
@@ -4452,7 +4455,7 @@
         <v>46225.862125590276</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>25</v>
@@ -4476,7 +4479,7 @@
         <v>26</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4489,7 +4492,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46225.86201641204</v>
@@ -4505,10 +4508,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46262</v>
@@ -4526,13 +4529,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="5">
         <v>46266</v>
@@ -4547,12 +4550,12 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="9">
         <v>46225.86202538194</v>
@@ -4562,16 +4565,16 @@
         <v>46225.86836851852</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4589,13 +4592,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q53" s="9">
         <v>46273</v>
@@ -4610,12 +4613,12 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46225.86203225695</v>
@@ -4625,16 +4628,16 @@
         <v>46238.487257870365</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46267</v>
@@ -4652,13 +4655,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4668,7 +4671,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B55" s="9">
         <v>46225.86204296297</v>
@@ -4678,16 +4681,16 @@
         <v>46238.48725839121</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I55" s="9">
         <v>46267</v>
@@ -4705,13 +4708,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4721,7 +4724,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46225.862053379635</v>
@@ -4731,16 +4734,16 @@
         <v>46238.48725583333</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I56" s="5">
         <v>46267</v>
@@ -4758,13 +4761,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4774,7 +4777,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B57" s="9">
         <v>46225.86206356481</v>
@@ -4784,16 +4787,16 @@
         <v>46225.870545729165</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I57" s="9">
         <v>46267</v>
@@ -4811,13 +4814,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4827,7 +4830,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B58" s="5">
         <v>46225.86208298611</v>
@@ -4837,16 +4840,16 @@
         <v>46225.86841018518</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -4864,13 +4867,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q58" s="5">
         <v>46274</v>
@@ -4885,12 +4888,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46225.862089999995</v>
@@ -4900,16 +4903,16 @@
         <v>46238.487258877314</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I59" s="9">
         <v>46274</v>
@@ -4927,13 +4930,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4943,7 +4946,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46225.86209783565</v>
@@ -4953,16 +4956,16 @@
         <v>46238.48726738426</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I60" s="5">
         <v>46274</v>
@@ -4980,13 +4983,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4996,7 +4999,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46225.86210570602</v>
@@ -5006,16 +5009,16 @@
         <v>46238.48725643518</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I61" s="9">
         <v>46274</v>
@@ -5033,13 +5036,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5049,7 +5052,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B62" s="5">
         <v>46225.86216362269</v>
@@ -5059,16 +5062,16 @@
         <v>46225.870609791666</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5086,13 +5089,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5102,7 +5105,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" s="9">
         <v>46225.86219280092</v>
@@ -5112,7 +5115,7 @@
         <v>46225.86232971065</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -5136,7 +5139,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5149,7 +5152,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>46225.86219668981</v>
@@ -5159,16 +5162,16 @@
         <v>46232.19127755787</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I64" s="5">
         <v>46230</v>
@@ -5186,13 +5189,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="5">
         <v>46231</v>
@@ -5207,12 +5210,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B65" s="9">
         <v>46225.86220582176</v>
@@ -5222,16 +5225,16 @@
         <v>46232.19127729167</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I65" s="9">
         <v>46230</v>
@@ -5249,13 +5252,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="9">
         <v>46231</v>
@@ -5270,12 +5273,12 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
         <v>46225.86221482639</v>
@@ -5285,16 +5288,16 @@
         <v>46232.19127710648</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5312,13 +5315,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5333,12 +5336,12 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B67" s="9">
         <v>46225.862222800926</v>
@@ -5348,7 +5351,7 @@
         <v>46232.60338638889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>25</v>
@@ -5372,7 +5375,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>26</v>
@@ -5385,7 +5388,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B68" s="5">
         <v>46225.862226516205</v>
@@ -5395,7 +5398,7 @@
         <v>46232.62438219908</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5422,13 +5425,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q68" s="5">
         <v>46281</v>
@@ -5443,12 +5446,12 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B69" s="9">
         <v>46225.862234050925</v>
@@ -5458,7 +5461,7 @@
         <v>46225.870632060185</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5485,13 +5488,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5501,7 +5504,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
         <v>46225.86224180556</v>
@@ -5511,7 +5514,7 @@
         <v>46225.87064059028</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5538,13 +5541,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5554,7 +5557,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B71" s="9">
         <v>46225.862249224534</v>
@@ -5564,7 +5567,7 @@
         <v>46225.87065297454</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5591,13 +5594,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5607,7 +5610,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B72" s="5">
         <v>46225.86225659722</v>
@@ -5617,7 +5620,7 @@
         <v>46225.87067319444</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5644,13 +5647,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5660,7 +5663,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B73" s="9">
         <v>46225.862276388885</v>
@@ -5670,7 +5673,7 @@
         <v>46232.624382141206</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5697,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q73" s="9">
         <v>46286</v>
@@ -5718,12 +5721,12 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B74" s="5">
         <v>46225.862283842594</v>
@@ -5733,7 +5736,7 @@
         <v>46238.48726658565</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5758,13 +5761,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5774,7 +5777,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B75" s="9">
         <v>46225.86229252315</v>
@@ -5784,7 +5787,7 @@
         <v>46238.487257326386</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5809,13 +5812,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5825,7 +5828,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B76" s="5">
         <v>46225.862306932875</v>
@@ -5835,7 +5838,7 @@
         <v>46238.48726778935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5860,13 +5863,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5876,7 +5879,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B77" s="9">
         <v>46225.86231524305</v>
@@ -5886,7 +5889,7 @@
         <v>46225.870728344904</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5911,13 +5914,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5927,7 +5930,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B78" s="5">
         <v>46225.862381087965</v>
@@ -5937,7 +5940,7 @@
         <v>46232.62438238426</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5964,13 +5967,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q78" s="5">
         <v>46287</v>
@@ -5985,12 +5988,12 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B79" s="9">
         <v>46225.862389155096</v>
@@ -6000,7 +6003,7 @@
         <v>46225.870759178244</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6027,13 +6030,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6043,7 +6046,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
         <v>46225.86239770833</v>
@@ -6053,7 +6056,7 @@
         <v>46225.870777442135</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6080,13 +6083,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6096,7 +6099,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B81" s="9">
         <v>46225.86240878473</v>
@@ -6106,7 +6109,7 @@
         <v>46225.870787824075</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6133,13 +6136,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6149,7 +6152,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46225.86241983796</v>
@@ -6159,7 +6162,7 @@
         <v>46225.87080640046</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6186,13 +6189,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6202,7 +6205,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B83" s="9">
         <v>46225.86244091435</v>
@@ -6212,7 +6215,7 @@
         <v>46240.82253846065</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6239,13 +6242,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q83" s="9">
         <v>46288</v>
@@ -6260,12 +6263,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B84" s="5">
         <v>46225.86244844907</v>
@@ -6275,7 +6278,7 @@
         <v>46238.48726703704</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6302,13 +6305,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6318,7 +6321,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B85" s="9">
         <v>46225.86245663195</v>
@@ -6328,7 +6331,7 @@
         <v>46238.48725680556</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6355,13 +6358,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6371,7 +6374,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B86" s="5">
         <v>46225.862464502316</v>
@@ -6381,7 +6384,7 @@
         <v>46225.870855393514</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6408,13 +6411,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6424,7 +6427,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B87" s="9">
         <v>46225.86247284722</v>
@@ -6434,7 +6437,7 @@
         <v>46225.87086599537</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6461,13 +6464,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6477,7 +6480,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B88" s="5">
         <v>46225.86249337963</v>
@@ -6487,7 +6490,7 @@
         <v>46240.8225384375</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6514,13 +6517,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q88" s="5">
         <v>46289</v>
@@ -6535,12 +6538,12 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B89" s="9">
         <v>46225.862501435186</v>
@@ -6550,7 +6553,7 @@
         <v>46225.87089600695</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6577,13 +6580,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6593,7 +6596,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B90" s="5">
         <v>46225.8625115162</v>
@@ -6603,7 +6606,7 @@
         <v>46225.87090469907</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6630,13 +6633,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6646,7 +6649,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B91" s="9">
         <v>46225.8625234375</v>
@@ -6656,7 +6659,7 @@
         <v>46225.870913969906</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6683,13 +6686,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6699,7 +6702,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B92" s="5">
         <v>46225.86257370371</v>
@@ -6709,7 +6712,7 @@
         <v>46225.870925243056</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6736,13 +6739,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6752,7 +6755,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B93" s="9">
         <v>46225.86260116898</v>
@@ -6762,7 +6765,7 @@
         <v>46232.62438732639</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6789,10 +6792,10 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6810,12 +6813,12 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B94" s="5">
         <v>46225.8626096875</v>
@@ -6825,7 +6828,7 @@
         <v>46225.87095484954</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6852,13 +6855,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6868,7 +6871,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B95" s="9">
         <v>46225.86261736111</v>
@@ -6878,7 +6881,7 @@
         <v>46225.87096165509</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6905,13 +6908,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6921,7 +6924,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B96" s="5">
         <v>46225.86262487269</v>
@@ -6931,7 +6934,7 @@
         <v>46225.87097416667</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6958,13 +6961,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6974,7 +6977,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B97" s="9">
         <v>46225.862632268516</v>
@@ -6984,7 +6987,7 @@
         <v>46225.870994074074</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7011,13 +7014,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7027,7 +7030,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B98" s="5">
         <v>46225.86265351852</v>
@@ -7037,7 +7040,7 @@
         <v>46225.86288905093</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>25</v>
@@ -7061,7 +7064,7 @@
         <v>26</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>26</v>
@@ -7074,7 +7077,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B99" s="9">
         <v>46225.86265758102</v>
@@ -7084,16 +7087,16 @@
         <v>46225.86992599537</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I99" s="9">
         <v>46294</v>
@@ -7111,13 +7114,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q99" s="9">
         <v>46294</v>
@@ -7132,12 +7135,12 @@
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B100" s="5">
         <v>46225.86266576389</v>
@@ -7147,16 +7150,16 @@
         <v>46225.87103081019</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I100" s="5">
         <v>46294</v>
@@ -7174,13 +7177,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7190,7 +7193,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B101" s="9">
         <v>46225.86267326389</v>
@@ -7200,16 +7203,16 @@
         <v>46225.87104060185</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I101" s="9">
         <v>46294</v>
@@ -7227,13 +7230,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7243,7 +7246,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B102" s="5">
         <v>46225.86268015046</v>
@@ -7253,16 +7256,16 @@
         <v>46225.87104780093</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I102" s="5">
         <v>46294</v>
@@ -7280,13 +7283,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7296,7 +7299,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B103" s="9">
         <v>46225.862687326386</v>
@@ -7306,16 +7309,16 @@
         <v>46225.871064861116</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I103" s="9">
         <v>46294</v>
@@ -7333,13 +7336,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7349,7 +7352,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B104" s="5">
         <v>46225.86270745371</v>
@@ -7359,7 +7362,7 @@
         <v>46225.86997988426</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7386,10 +7389,10 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>26</v>
@@ -7407,12 +7410,12 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B105" s="9">
         <v>46225.8627578125</v>
@@ -7422,7 +7425,7 @@
         <v>46225.87109706018</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7449,13 +7452,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7465,7 +7468,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B106" s="5">
         <v>46225.86276570601</v>
@@ -7475,7 +7478,7 @@
         <v>46225.871105266204</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7502,13 +7505,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7518,7 +7521,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B107" s="9">
         <v>46225.86277225694</v>
@@ -7528,7 +7531,7 @@
         <v>46225.87111719907</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7555,13 +7558,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7571,7 +7574,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B108" s="5">
         <v>46225.86277868056</v>
@@ -7581,7 +7584,7 @@
         <v>46225.8711331713</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7608,13 +7611,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7624,7 +7627,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B109" s="9">
         <v>46225.8627980787</v>
@@ -7634,16 +7637,16 @@
         <v>46225.870042650466</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I109" s="9">
         <v>46296</v>
@@ -7661,13 +7664,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q109" s="9">
         <v>46296</v>
@@ -7682,12 +7685,12 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B110" s="5">
         <v>46225.86280646991</v>
@@ -7697,16 +7700,16 @@
         <v>46225.87116359954</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I110" s="5">
         <v>46296</v>
@@ -7724,13 +7727,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7740,7 +7743,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B111" s="9">
         <v>46225.8628134375</v>
@@ -7750,16 +7753,16 @@
         <v>46225.87117237269</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I111" s="9">
         <v>46296</v>
@@ -7777,13 +7780,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7793,7 +7796,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B112" s="5">
         <v>46225.86282005787</v>
@@ -7803,16 +7806,16 @@
         <v>46225.8711906713</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I112" s="5">
         <v>46296</v>
@@ -7830,13 +7833,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7846,7 +7849,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B113" s="9">
         <v>46225.862826516204</v>
@@ -7856,16 +7859,16 @@
         <v>46225.87120541667</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I113" s="9">
         <v>46296</v>
@@ -7883,13 +7886,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7899,7 +7902,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B114" s="5">
         <v>46225.86284444445</v>
@@ -7909,16 +7912,16 @@
         <v>46225.87010216435</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I114" s="5">
         <v>46297</v>
@@ -7936,13 +7939,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q114" s="5">
         <v>46297</v>
@@ -7957,12 +7960,12 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B115" s="9">
         <v>46225.86285697916</v>
@@ -7972,16 +7975,16 @@
         <v>46225.87123498843</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I115" s="9">
         <v>46297</v>
@@ -7999,13 +8002,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8015,7 +8018,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B116" s="5">
         <v>46225.862862939815</v>
@@ -8025,16 +8028,16 @@
         <v>46225.87124284722</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I116" s="5">
         <v>46297</v>
@@ -8052,13 +8055,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8068,7 +8071,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B117" s="9">
         <v>46225.86286878472</v>
@@ -8078,16 +8081,16 @@
         <v>46225.87125150463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I117" s="9">
         <v>46297</v>
@@ -8105,13 +8108,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8121,7 +8124,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B118" s="5">
         <v>46225.86287459491</v>
@@ -8131,16 +8134,16 @@
         <v>46225.87127599537</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I118" s="5">
         <v>46297</v>
@@ -8158,13 +8161,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8174,7 +8177,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B119" s="9">
         <v>46225.862925532405</v>
@@ -8184,7 +8187,7 @@
         <v>46225.86295643519</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>25</v>
@@ -8208,7 +8211,7 @@
         <v>26</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>26</v>
@@ -8221,7 +8224,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B120" s="5">
         <v>46225.862929201394</v>
@@ -8231,16 +8234,16 @@
         <v>46225.86295732639</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I120" s="5">
         <v>46300</v>
@@ -8258,13 +8261,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q120" s="5">
         <v>46304</v>
@@ -8279,12 +8282,12 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B121" s="9">
         <v>46225.86294039352</v>
@@ -8294,7 +8297,7 @@
         <v>46225.86295819444</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8321,13 +8324,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q121" s="9">
         <v>46304</v>
@@ -8342,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="U121" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -4076,7 +4076,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46225.866340925924</v>
+        <v>46253.18211637731</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>161</v>
@@ -4118,8 +4118,8 @@
       <c r="R45" s="9">
         <v>46260</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>32</v>
+      <c r="S45" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46225.8663590625</v>
+        <v>46253.182116296295</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4181,8 +4181,8 @@
       <c r="R46" s="5">
         <v>46260</v>
       </c>
-      <c r="S46" s="7" t="s">
-        <v>32</v>
+      <c r="S46" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46225.86637913194</v>
+        <v>46253.18211689815</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>169</v>
@@ -4244,8 +4244,8 @@
       <c r="R47" s="9">
         <v>46260</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>32</v>
+      <c r="S47" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46225.866400115745</v>
+        <v>46254.17654792824</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4307,8 +4307,8 @@
       <c r="R48" s="5">
         <v>46261</v>
       </c>
-      <c r="S48" s="7" t="s">
-        <v>32</v>
+      <c r="S48" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46225.86644668982</v>
+        <v>46254.176547662035</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>175</v>
@@ -4370,8 +4370,8 @@
       <c r="R49" s="9">
         <v>46261</v>
       </c>
-      <c r="S49" s="7" t="s">
-        <v>32</v>
+      <c r="S49" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46225.86650415509</v>
+        <v>46254.17654818287</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>177</v>
@@ -4433,8 +4433,8 @@
       <c r="R50" s="5">
         <v>46261</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>32</v>
+      <c r="S50" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -441,7 +441,7 @@
     <t xml:space="preserve">Generacion Oc OT 4376 OT 4381  </t>
   </si>
   <si>
-    <t xml:space="preserve">propuesta fabricación externa </t>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
   </si>
   <si>
     <t xml:space="preserve">Armado  OT 4381 ,Fabricación externa   OT 4381  </t>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46237.553715648144</v>
+        <v>46254.64730815972</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46254.64730815972</v>
+        <v>46255.17040880787</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46255.17040880787</v>
+        <v>46255.62865344908</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46252.17149778936</v>
+        <v>46259.16936681713</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46225.867042893515</v>
+        <v>46259.16936259259</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46252.171497881944</v>
+        <v>46259.16936540509</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>98</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46225.8671391088</v>
+        <v>46259.16936804398</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>103</v>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46252.17149795139</v>
+        <v>46259.1693640625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>106</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46225.86721106482</v>
+        <v>46259.16936925926</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>111</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46225.867920069446</v>
+        <v>46259.16850719907</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>78</v>
@@ -4543,8 +4543,8 @@
       <c r="R52" s="5">
         <v>46262</v>
       </c>
-      <c r="S52" s="7" t="s">
-        <v>32</v>
+      <c r="S52" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -348,232 +348,232 @@
     <t xml:space="preserve">Generación OC corte laser   OT 4381 ,Fabricacion corte laser  OT 4381 </t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1216803783052320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC corte laser   OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte Laser   OT 4381 ,Fabricacion corte laser  OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803783052346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion corte laser  OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   OT 4381  ,Corte Laser   OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803854924558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte plasma   OT 4381  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación corte plasma   OT 4381 ,Generacion OC Corte plasma   OT 4381 </t>
+  </si>
+  <si>
+    <t>1216804002762799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación corte plasma   OT 4381 ,Corte plasma   OT 4381  </t>
+  </si>
+  <si>
+    <t>1216804002762822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación corte plasma   OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte plasma   OT 4381  ,Corte plasma   OT 4381  </t>
+  </si>
+  <si>
+    <t>1216803783062075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado  OT 4381  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Mecanizado  OT 4381 ,Generación OC mecanizado  OT 4381 </t>
+  </si>
+  <si>
+    <t>1216804002803579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Mecanizado  OT 4381 ,Mecanizado  OT 4381  </t>
+  </si>
+  <si>
+    <t>1216804002803602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Mecanizado  OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado  OT 4381  ,Recepcion mecanizado  OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803783135442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa   OT 4381  </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado  OT 4381 ,Control de calidad   OT 4381  ,Generacion Oc OT 4376 OT 4381  </t>
+  </si>
+  <si>
+    <t>1216804002821581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc OT 4376 OT 4381  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado  OT 4381 ,Fabricación externa   OT 4381  </t>
+  </si>
+  <si>
+    <t>1216804002821604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado  OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa   OT 4381  ,Control de calidad   OT 4381  </t>
+  </si>
+  <si>
+    <t>1216803783138260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad   OT 4381  </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216803961636526</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check pruebas FAT  OT 4381  ,Plano Definitivos  OT 4381 ,Check Planos  OT 4381 ,Plano Preliminar  OT 4381  </t>
+  </si>
+  <si>
+    <t>1216803961636538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Preliminar  OT 4381  </t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Plano Definitivos  OT 4381 ,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1216804002837885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos  OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos  OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803961645389</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Propuesta Fabricación externa   OT 4381  ,Propuesta Mecanizado  OT 4381  ,Propuesta Corte plasma   OT 4381  ,propuesta Corte laser  OT 4381  ,Ingenieria y diseñoo:,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803854997633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check pruebas FAT  OT 4381  </t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803854997656</t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Check pruebas FAT  OT 4381  </t>
+  </si>
+  <si>
+    <t>1216804002872345</t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4347 Preparación Materiales,Check pruebas FAT  OT 4381  ,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1216803855027309</t>
+  </si>
+  <si>
+    <t>1216803855027327</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT  OT 4381  ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803783195507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   OT 4381  ,Control de calidad Mecanizado  OT 4381  ,Recepcion corte plasma   OT 4381  ,Recepcion mecanizado  OT 4381 ,Control de calidad corte Laser OT 4381  ,Control de calidad Corte plasma  OT 4381  </t>
+  </si>
+  <si>
+    <t>1216803783195519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser   OT 4381  </t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad corte Laser OT 4381  </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1216803783052320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC corte laser   OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte Laser   OT 4381 ,Fabricacion corte laser  OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803783052346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion corte laser  OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   OT 4381  ,Corte Laser   OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803854924558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte plasma   OT 4381  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación corte plasma   OT 4381 ,Generacion OC Corte plasma   OT 4381 </t>
-  </si>
-  <si>
-    <t>1216804002762799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación corte plasma   OT 4381 ,Corte plasma   OT 4381  </t>
-  </si>
-  <si>
-    <t>1216804002762822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación corte plasma   OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte plasma   OT 4381  ,Corte plasma   OT 4381  </t>
-  </si>
-  <si>
-    <t>1216803783062075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado  OT 4381  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Mecanizado  OT 4381 ,Generación OC mecanizado  OT 4381 </t>
-  </si>
-  <si>
-    <t>1216804002803579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Mecanizado  OT 4381 ,Mecanizado  OT 4381  </t>
-  </si>
-  <si>
-    <t>1216804002803602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Mecanizado  OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado  OT 4381  ,Recepcion mecanizado  OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803783135442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa   OT 4381  </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado  OT 4381 ,Control de calidad   OT 4381  ,Generacion Oc OT 4376 OT 4381  </t>
-  </si>
-  <si>
-    <t>1216804002821581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc OT 4376 OT 4381  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado  OT 4381 ,Fabricación externa   OT 4381  </t>
-  </si>
-  <si>
-    <t>1216804002821604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado  OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa   OT 4381  ,Control de calidad   OT 4381  </t>
-  </si>
-  <si>
-    <t>1216803783138260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad   OT 4381  </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216803961636526</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check pruebas FAT  OT 4381  ,Plano Definitivos  OT 4381 ,Check Planos  OT 4381 ,Plano Preliminar  OT 4381  </t>
-  </si>
-  <si>
-    <t>1216803961636538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Preliminar  OT 4381  </t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Plano Definitivos  OT 4381 ,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1216804002837885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos  OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos  OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803961645389</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Propuesta Fabricación externa   OT 4381  ,Propuesta Mecanizado  OT 4381  ,Propuesta Corte plasma   OT 4381  ,propuesta Corte laser  OT 4381  ,Ingenieria y diseñoo:,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803854997633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check pruebas FAT  OT 4381  </t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803854997656</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Check pruebas FAT  OT 4381  </t>
-  </si>
-  <si>
-    <t>1216804002872345</t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4347 Preparación Materiales,Check pruebas FAT  OT 4381  ,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1216803855027309</t>
-  </si>
-  <si>
-    <t>1216803855027327</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT  OT 4381  ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803783195507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   OT 4381  ,Control de calidad Mecanizado  OT 4381  ,Recepcion corte plasma   OT 4381  ,Recepcion mecanizado  OT 4381 ,Control de calidad corte Laser OT 4381  ,Control de calidad Corte plasma  OT 4381  </t>
-  </si>
-  <si>
-    <t>1216803783195519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser   OT 4381  </t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad corte Laser OT 4381  </t>
   </si>
   <si>
     <t>1216803783211225</t>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46259.16936681713</v>
+        <v>46260.19914571759</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -2823,19 +2823,19 @@
       <c r="R22" s="5">
         <v>46247</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>89</v>
+      <c r="S22" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="9">
         <v>46225.86167825232</v>
@@ -2845,7 +2845,7 @@
         <v>46248.171457476856</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2878,7 +2878,7 @@
         <v>68</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2889,12 +2889,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46225.86168543981</v>
@@ -2904,7 +2904,7 @@
         <v>46259.16936259259</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2934,10 +2934,10 @@
         <v>84</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2948,22 +2948,22 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="9">
         <v>46225.86169273148</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46259.16936540509</v>
+        <v>46260.19914502314</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -2993,7 +2993,7 @@
         <v>83</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3004,19 +3004,19 @@
       <c r="R25" s="9">
         <v>46247</v>
       </c>
-      <c r="S25" s="12" t="s">
-        <v>89</v>
+      <c r="S25" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46225.86169921297</v>
@@ -3053,13 +3053,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3069,7 +3069,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B27" s="9">
         <v>46225.86170601852</v>
@@ -3079,7 +3079,7 @@
         <v>46259.16936804398</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3106,13 +3106,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>75</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3122,17 +3122,17 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46225.86175964121</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46259.1693640625</v>
+        <v>46260.19914489583</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3162,7 +3162,7 @@
         <v>83</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3173,19 +3173,19 @@
       <c r="R28" s="5">
         <v>46247</v>
       </c>
-      <c r="S28" s="12" t="s">
-        <v>89</v>
+      <c r="S28" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="9">
         <v>46225.861767326394</v>
@@ -3222,13 +3222,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>80</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B30" s="5">
         <v>46225.8617740162</v>
@@ -3248,7 +3248,7 @@
         <v>46259.16936925926</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3275,13 +3275,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3291,7 +3291,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="9">
         <v>46225.86178056713</v>
@@ -3301,16 +3301,16 @@
         <v>46225.866204108796</v>
       </c>
       <c r="E31" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
+      <c r="H31" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3331,7 +3331,7 @@
         <v>83</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
@@ -3349,12 +3349,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46225.8617949537</v>
@@ -3364,16 +3364,16 @@
         <v>46255.62865344908</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>46247</v>
@@ -3391,13 +3391,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O32" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B33" s="9">
         <v>46225.86180262732</v>
@@ -3417,16 +3417,16 @@
         <v>46225.86759815972</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I33" s="9">
         <v>46258</v>
@@ -3444,13 +3444,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46225.8618097338</v>
@@ -3470,16 +3470,16 @@
         <v>46225.867627534724</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3497,13 +3497,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B35" s="9">
         <v>46225.86181672454</v>
@@ -3523,7 +3523,7 @@
         <v>46238.48726621528</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3547,7 +3547,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46225.86182068287</v>
@@ -3572,16 +3572,16 @@
         <v>46235.207714502314</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3599,13 +3599,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>47</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3625,7 +3625,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B37" s="9">
         <v>46225.86182918982</v>
@@ -3637,16 +3637,16 @@
         <v>46242.20040111111</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3664,13 +3664,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46225.86183666666</v>
@@ -3708,10 +3708,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3729,13 +3729,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="9">
         <v>46225.86185291667</v>
@@ -3765,16 +3765,16 @@
         <v>46225.869796087965</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3792,13 +3792,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3813,12 +3813,12 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46225.86186070602</v>
@@ -3828,16 +3828,16 @@
         <v>46225.870297002315</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3853,13 +3853,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="P40" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="9">
         <v>46225.861866770836</v>
@@ -3879,16 +3879,16 @@
         <v>46225.870431400464</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3904,13 +3904,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46225.861897951385</v>
@@ -3930,16 +3930,16 @@
         <v>46225.87044054398</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="5">
@@ -3955,13 +3955,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="9">
         <v>46225.86190395833</v>
@@ -3981,16 +3981,16 @@
         <v>46225.87046690972</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -4006,13 +4006,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46225.86196252315</v>
@@ -4032,7 +4032,7 @@
         <v>46225.86211475694</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>25</v>
@@ -4056,7 +4056,7 @@
         <v>26</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4069,26 +4069,26 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="9">
         <v>46225.86196658565</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46253.18211637731</v>
+        <v>46260.16931907408</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I45" s="10"/>
       <c r="J45" s="9">
@@ -4104,13 +4104,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -4119,13 +4119,13 @@
         <v>46260</v>
       </c>
       <c r="S45" s="12" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46253.182116296295</v>
+        <v>46260.1693211574</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4146,10 +4146,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I46" s="5">
         <v>46260</v>
@@ -4167,10 +4167,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>167</v>
@@ -4182,13 +4182,13 @@
         <v>46260</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46253.18211689815</v>
+        <v>46260.16932237268</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>169</v>
@@ -4209,10 +4209,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I47" s="9">
         <v>46260</v>
@@ -4230,10 +4230,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>170</v>
@@ -4245,13 +4245,13 @@
         <v>46260</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4272,10 +4272,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4293,10 +4293,10 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>173</v>
@@ -4308,13 +4308,13 @@
         <v>46261</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4335,10 +4335,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="I49" s="9">
         <v>46261</v>
@@ -4356,7 +4356,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>166</v>
@@ -4371,13 +4371,13 @@
         <v>46261</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4398,10 +4398,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I50" s="5">
         <v>46261</v>
@@ -4419,7 +4419,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>169</v>
@@ -4434,13 +4434,13 @@
         <v>46261</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4544,13 +4544,13 @@
         <v>46262</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4595,7 +4595,7 @@
         <v>180</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>180</v>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4628,7 +4628,7 @@
         <v>46238.487257870365</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4681,7 +4681,7 @@
         <v>46238.48725839121</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4734,7 +4734,7 @@
         <v>46238.48725583333</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4787,7 +4787,7 @@
         <v>46225.870545729165</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4846,10 +4846,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I58" s="5">
         <v>46274</v>
@@ -4870,7 +4870,7 @@
         <v>180</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>180</v>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4903,16 +4903,16 @@
         <v>46238.487258877314</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="I59" s="9">
         <v>46274</v>
@@ -4956,16 +4956,16 @@
         <v>46238.48726738426</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I60" s="5">
         <v>46274</v>
@@ -5009,16 +5009,16 @@
         <v>46238.48725643518</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="I61" s="9">
         <v>46274</v>
@@ -5062,16 +5062,16 @@
         <v>46225.870609791666</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5092,7 +5092,7 @@
         <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>201</v>
@@ -5168,10 +5168,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I64" s="5">
         <v>46230</v>
@@ -5210,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5231,10 +5231,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I65" s="9">
         <v>46230</v>
@@ -5273,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5294,10 +5294,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5336,7 +5336,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5428,7 +5428,7 @@
         <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>223</v>
@@ -5446,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5461,7 +5461,7 @@
         <v>46225.870632060185</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5491,7 +5491,7 @@
         <v>222</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>225</v>
@@ -5514,7 +5514,7 @@
         <v>46225.87064059028</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5544,7 +5544,7 @@
         <v>222</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>227</v>
@@ -5567,7 +5567,7 @@
         <v>46225.87065297454</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5597,7 +5597,7 @@
         <v>222</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>229</v>
@@ -5620,7 +5620,7 @@
         <v>46225.87067319444</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5650,7 +5650,7 @@
         <v>222</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>231</v>
@@ -5721,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5736,7 +5736,7 @@
         <v>46238.48726658565</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5787,7 +5787,7 @@
         <v>46238.487257326386</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5838,7 +5838,7 @@
         <v>46238.48726778935</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5889,7 +5889,7 @@
         <v>46225.870728344904</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5917,7 +5917,7 @@
         <v>233</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>241</v>
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6003,7 +6003,7 @@
         <v>46225.870759178244</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6056,7 +6056,7 @@
         <v>46225.870777442135</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6109,7 +6109,7 @@
         <v>46225.870787824075</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6162,7 +6162,7 @@
         <v>46225.87080640046</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6192,7 +6192,7 @@
         <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>252</v>
@@ -6263,7 +6263,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6278,7 +6278,7 @@
         <v>46238.48726703704</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6331,7 +6331,7 @@
         <v>46238.48725680556</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6384,7 +6384,7 @@
         <v>46225.870855393514</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6437,7 +6437,7 @@
         <v>46225.87086599537</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6467,7 +6467,7 @@
         <v>256</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>265</v>
@@ -6520,7 +6520,7 @@
         <v>219</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>268</v>
@@ -6538,7 +6538,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
         <v>46225.87089600695</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6606,7 +6606,7 @@
         <v>46225.87090469907</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6659,7 +6659,7 @@
         <v>46225.870913969906</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6712,7 +6712,7 @@
         <v>46225.870925243056</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6742,7 +6742,7 @@
         <v>267</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>275</v>
@@ -6813,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -6828,7 +6828,7 @@
         <v>46225.87095484954</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6858,7 +6858,7 @@
         <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>279</v>
@@ -6881,7 +6881,7 @@
         <v>46225.87096165509</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6911,7 +6911,7 @@
         <v>268</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>281</v>
@@ -6934,7 +6934,7 @@
         <v>46225.87097416667</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6964,7 +6964,7 @@
         <v>268</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>281</v>
@@ -6987,7 +6987,7 @@
         <v>46225.870994074074</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7017,7 +7017,7 @@
         <v>268</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>279</v>
@@ -7117,7 +7117,7 @@
         <v>285</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>291</v>
@@ -7135,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7150,7 +7150,7 @@
         <v>46225.87103081019</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7180,7 +7180,7 @@
         <v>288</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>293</v>
@@ -7203,7 +7203,7 @@
         <v>46225.87104060185</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7233,7 +7233,7 @@
         <v>288</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>293</v>
@@ -7256,7 +7256,7 @@
         <v>46225.87104780093</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7286,7 +7286,7 @@
         <v>288</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>296</v>
@@ -7309,7 +7309,7 @@
         <v>46225.871064861116</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7339,7 +7339,7 @@
         <v>288</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>293</v>
@@ -7410,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7425,7 +7425,7 @@
         <v>46225.87109706018</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7455,7 +7455,7 @@
         <v>299</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>302</v>
@@ -7478,7 +7478,7 @@
         <v>46225.871105266204</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7508,7 +7508,7 @@
         <v>299</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>302</v>
@@ -7531,7 +7531,7 @@
         <v>46225.87111719907</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7561,7 +7561,7 @@
         <v>299</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>302</v>
@@ -7584,7 +7584,7 @@
         <v>46225.8711331713</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7614,7 +7614,7 @@
         <v>299</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>302</v>
@@ -7667,7 +7667,7 @@
         <v>285</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>285</v>
@@ -7685,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -7700,7 +7700,7 @@
         <v>46225.87116359954</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7730,7 +7730,7 @@
         <v>307</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>309</v>
@@ -7753,7 +7753,7 @@
         <v>46225.87117237269</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7783,7 +7783,7 @@
         <v>307</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>311</v>
@@ -7806,7 +7806,7 @@
         <v>46225.8711906713</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7836,7 +7836,7 @@
         <v>307</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>311</v>
@@ -7859,7 +7859,7 @@
         <v>46225.87120541667</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7889,7 +7889,7 @@
         <v>307</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>311</v>
@@ -7942,7 +7942,7 @@
         <v>285</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>316</v>
@@ -7960,7 +7960,7 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -7975,7 +7975,7 @@
         <v>46225.87123498843</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8005,7 +8005,7 @@
         <v>315</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>318</v>
@@ -8028,7 +8028,7 @@
         <v>46225.87124284722</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8058,7 +8058,7 @@
         <v>315</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>320</v>
@@ -8081,7 +8081,7 @@
         <v>46225.87125150463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8111,7 +8111,7 @@
         <v>315</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>320</v>
@@ -8134,7 +8134,7 @@
         <v>46225.87127599537</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8164,7 +8164,7 @@
         <v>315</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>315</v>
@@ -8282,7 +8282,7 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -8345,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="U121" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -573,34 +573,34 @@
     <t xml:space="preserve">Bodega ,Control de calidad corte Laser OT 4381  </t>
   </si>
   <si>
+    <t>1216803783211225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte plasma   OT 4381  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,Control de calidad Corte plasma  OT 4381  </t>
+  </si>
+  <si>
+    <t>1216804002965371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion mecanizado  OT 4381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado  OT 4381  ,Bodega </t>
+  </si>
+  <si>
+    <t>1216804002967580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte Laser OT 4381  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216803783211225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte plasma   OT 4381  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,Control de calidad Corte plasma  OT 4381  </t>
-  </si>
-  <si>
-    <t>1216804002965371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion mecanizado  OT 4381 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado  OT 4381  ,Bodega </t>
-  </si>
-  <si>
-    <t>1216804002967580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte Laser OT 4381  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega </t>
   </si>
   <si>
     <t>1216804002970940</t>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46225.86211475694</v>
+        <v>46261.50970834491</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>157</v>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46260.16931907408</v>
+        <v>46261.199512974534</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>160</v>
@@ -4118,8 +4118,8 @@
       <c r="R45" s="9">
         <v>46260</v>
       </c>
-      <c r="S45" s="12" t="s">
-        <v>164</v>
+      <c r="S45" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
@@ -4130,17 +4130,17 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46225.86197478009</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46260.1693211574</v>
+        <v>46261.19951315972</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4173,7 +4173,7 @@
         <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q46" s="5">
         <v>46260</v>
@@ -4181,8 +4181,8 @@
       <c r="R46" s="5">
         <v>46260</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>164</v>
+      <c r="S46" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4193,17 +4193,17 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="9">
         <v>46225.86198239583</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46260.16932237268</v>
+        <v>46261.199514293985</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4236,7 +4236,7 @@
         <v>110</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="9">
         <v>46260</v>
@@ -4244,8 +4244,8 @@
       <c r="R47" s="9">
         <v>46260</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>164</v>
+      <c r="S47" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>
@@ -4256,17 +4256,17 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46225.86198986111</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46254.17654792824</v>
+        <v>46261.168797453705</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4299,7 +4299,7 @@
         <v>160</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4308,7 +4308,7 @@
         <v>46261</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4324,9 +4324,11 @@
       <c r="B49" s="9">
         <v>46225.86199775463</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46261.509700509254</v>
+      </c>
       <c r="D49" s="9">
-        <v>46254.176547662035</v>
+        <v>46261.50971637732</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>175</v>
@@ -4359,10 +4361,10 @@
         <v>157</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q49" s="9">
         <v>46261</v>
@@ -4371,13 +4373,13 @@
         <v>46261</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="T49" s="10">
-        <v>0</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>89</v>
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4389,7 +4391,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46254.17654818287</v>
+        <v>46261.168800949075</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>177</v>
@@ -4422,7 +4424,7 @@
         <v>157</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>178</v>
@@ -4434,7 +4436,7 @@
         <v>46261</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4544,7 +4546,7 @@
         <v>46262</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4625,7 +4627,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46238.487257870365</v>
+        <v>46261.50970738426</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>149</v>
@@ -4678,7 +4680,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46238.48725839121</v>
+        <v>46261.509707743055</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>149</v>
@@ -4731,7 +4733,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46238.48725583333</v>
+        <v>46261.509706701385</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>149</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -600,43 +600,43 @@
     <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega </t>
   </si>
   <si>
+    <t>1216804002970940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma  OT 4381  </t>
+  </si>
+  <si>
+    <t>1216804002970968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado  OT 4381  </t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803855110759</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparacion materiales  OT 4381  ,Armado OT 4381 ,Control de calidad Armado OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803855125428</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Caldereria,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216804002970940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma  OT 4381  </t>
-  </si>
-  <si>
-    <t>1216804002970968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado  OT 4381  </t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803855110759</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparacion materiales  OT 4381  ,Armado OT 4381 ,Control de calidad Armado OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803855125428</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1216803855133959</t>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46261.168797453705</v>
+        <v>46262.18550431713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -4307,8 +4307,8 @@
       <c r="R48" s="5">
         <v>46261</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>173</v>
+      <c r="S48" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" s="9">
         <v>46225.86199775463</v>
@@ -4328,10 +4328,10 @@
         <v>46261.509700509254</v>
       </c>
       <c r="D49" s="9">
-        <v>46261.50971637732</v>
+        <v>46262.18550420139</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4372,8 +4372,8 @@
       <c r="R49" s="9">
         <v>46261</v>
       </c>
-      <c r="S49" s="12" t="s">
-        <v>173</v>
+      <c r="S49" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4384,17 +4384,17 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46225.86200543982</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46261.168800949075</v>
+        <v>46262.18550445602</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4427,7 +4427,7 @@
         <v>168</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="5">
         <v>46261</v>
@@ -4435,8 +4435,8 @@
       <c r="R50" s="5">
         <v>46261</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>173</v>
+      <c r="S50" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B51" s="9">
         <v>46225.86201293982</v>
@@ -4457,7 +4457,7 @@
         <v>46225.862125590276</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>25</v>
@@ -4481,7 +4481,7 @@
         <v>26</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46225.86201641204</v>
@@ -4510,10 +4510,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46262</v>
@@ -4531,13 +4531,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q52" s="5">
         <v>46266</v>
@@ -4546,7 +4546,7 @@
         <v>46262</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4573,10 +4573,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4594,13 +4594,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>147</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q53" s="9">
         <v>46273</v>
@@ -4636,10 +4636,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46267</v>
@@ -4689,10 +4689,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I55" s="9">
         <v>46267</v>
@@ -4742,10 +4742,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I56" s="5">
         <v>46267</v>
@@ -4795,10 +4795,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I57" s="9">
         <v>46267</v>
@@ -4869,13 +4869,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>147</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q58" s="5">
         <v>46274</v>
@@ -7645,10 +7645,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I109" s="9">
         <v>46296</v>
@@ -7708,10 +7708,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I110" s="5">
         <v>46296</v>
@@ -7761,10 +7761,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I111" s="9">
         <v>46296</v>
@@ -7814,10 +7814,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I112" s="5">
         <v>46296</v>
@@ -7867,10 +7867,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H113" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I113" s="9">
         <v>46296</v>
@@ -7920,10 +7920,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I114" s="5">
         <v>46297</v>
@@ -7983,10 +7983,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I115" s="9">
         <v>46297</v>
@@ -8036,10 +8036,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I116" s="5">
         <v>46297</v>
@@ -8089,10 +8089,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I117" s="9">
         <v>46297</v>
@@ -8142,10 +8142,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I118" s="5">
         <v>46297</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -4501,7 +4501,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46259.16850719907</v>
+        <v>46266.169597500004</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>78</v>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46225.86836851852</v>
+        <v>46266.20217431713</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>187</v>
@@ -4608,8 +4608,8 @@
       <c r="R53" s="9">
         <v>46267</v>
       </c>
-      <c r="S53" s="7" t="s">
-        <v>32</v>
+      <c r="S53" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -636,13 +636,13 @@
     <t>Caldereria,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
+    <t>1216803855133959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado OT 4381 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216803855133959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado OT 4381 </t>
   </si>
   <si>
     <t>1216803855133982</t>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46266.169597500004</v>
+        <v>46267.199387870365</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>78</v>
@@ -4545,8 +4545,8 @@
       <c r="R52" s="5">
         <v>46262</v>
       </c>
-      <c r="S52" s="12" t="s">
-        <v>185</v>
+      <c r="S52" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="9">
         <v>46225.86202538194</v>
@@ -4567,7 +4567,7 @@
         <v>46266.20217431713</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4609,7 +4609,7 @@
         <v>46267</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4657,7 +4657,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>189</v>
@@ -4710,7 +4710,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>192</v>
@@ -4763,7 +4763,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>195</v>
@@ -4816,7 +4816,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>78</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46225.86841018518</v>
+        <v>46267.17894387731</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>198</v>
@@ -4883,8 +4883,8 @@
       <c r="R58" s="5">
         <v>46274</v>
       </c>
-      <c r="S58" s="7" t="s">
-        <v>32</v>
+      <c r="S58" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46266.20217431713</v>
+        <v>46273.168693680556</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>186</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46261.50970738426</v>
+        <v>46273.168695127315</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>149</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46261.509707743055</v>
+        <v>46273.16869601852</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>149</v>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46261.509706701385</v>
+        <v>46273.16869688657</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>149</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46225.870545729165</v>
+        <v>46273.168692708336</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>149</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -642,40 +642,40 @@
     <t xml:space="preserve">Armado OT 4381 </t>
   </si>
   <si>
+    <t>1216803855133982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado  OT 4381  ,Control de calidad corte Laser OT 4381  ,Control de calidad Corte plasma  OT 4381  ,Check Planos  OT 4381 ,Preparacion materiales  OT 4381  </t>
+  </si>
+  <si>
+    <t>Armado OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803882595073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Planos  OT 4381 ,Preparacion materiales  OT 4381  ,Control de calidad Mecanizado  OT 4381  ,Control de calidad corte Laser OT 4381  ,Control de calidad Corte plasma  OT 4381  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Armado OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803961763691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma  OT 4381  ,Control de calidad Mecanizado  OT 4381  ,Check Planos  OT 4381 ,Preparacion materiales  OT 4381  ,Control de calidad corte Laser OT 4381  </t>
+  </si>
+  <si>
+    <t>1216803783264906</t>
+  </si>
+  <si>
+    <t>1216803961773636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado OT 4381 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216803855133982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado  OT 4381  ,Control de calidad corte Laser OT 4381  ,Control de calidad Corte plasma  OT 4381  ,Check Planos  OT 4381 ,Preparacion materiales  OT 4381  </t>
-  </si>
-  <si>
-    <t>Armado OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803882595073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Planos  OT 4381 ,Preparacion materiales  OT 4381  ,Control de calidad Mecanizado  OT 4381  ,Control de calidad corte Laser OT 4381  ,Control de calidad Corte plasma  OT 4381  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Armado OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803961763691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma  OT 4381  ,Control de calidad Mecanizado  OT 4381  ,Check Planos  OT 4381 ,Preparacion materiales  OT 4381  ,Control de calidad corte Laser OT 4381  </t>
-  </si>
-  <si>
-    <t>1216803783264906</t>
-  </si>
-  <si>
-    <t>1216803961773636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado OT 4381 </t>
   </si>
   <si>
     <t>1216803961773659</t>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46273.168693680556</v>
+        <v>46274.141876608795</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>186</v>
@@ -4608,8 +4608,8 @@
       <c r="R53" s="9">
         <v>46267</v>
       </c>
-      <c r="S53" s="12" t="s">
-        <v>187</v>
+      <c r="S53" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4620,7 +4620,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46225.86203225695</v>
@@ -4660,10 +4660,10 @@
         <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4673,7 +4673,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B55" s="9">
         <v>46225.86204296297</v>
@@ -4713,10 +4713,10 @@
         <v>186</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46225.862053379635</v>
@@ -4766,10 +4766,10 @@
         <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4779,7 +4779,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B57" s="9">
         <v>46225.86206356481</v>
@@ -4822,7 +4822,7 @@
         <v>78</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4832,17 +4832,17 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B58" s="5">
         <v>46225.86208298611</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46267.17894387731</v>
+        <v>46274.16866657407</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4884,7 +4884,7 @@
         <v>46274</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46238.487258877314</v>
+        <v>46274.16866800926</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>149</v>
@@ -4932,7 +4932,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>200</v>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46238.48726738426</v>
+        <v>46274.168665474535</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>149</v>
@@ -4985,7 +4985,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>200</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46238.48725643518</v>
+        <v>46274.168669108796</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>149</v>
@@ -5038,7 +5038,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>205</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46225.870609791666</v>
+        <v>46274.16866429398</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>149</v>
@@ -5091,7 +5091,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>149</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46232.62438219908</v>
+        <v>46274.146724861115</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>222</v>
@@ -5441,8 +5441,8 @@
       <c r="R68" s="5">
         <v>46275</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>32</v>
+      <c r="S68" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>

--- a/data/50001582 - XEMORTIZ LA CANTERA.xlsx
+++ b/data/50001582 - XEMORTIZ LA CANTERA.xlsx
@@ -675,82 +675,82 @@
     <t xml:space="preserve">Control de calidad Armado OT 4381 </t>
   </si>
   <si>
+    <t>1216803961773659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Check Planos  OT 4381 </t>
+  </si>
+  <si>
+    <t>Control de calidad Armado OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803882614137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Control de calidad Armado OT 4381 </t>
+  </si>
+  <si>
+    <t>1216804003009895</t>
+  </si>
+  <si>
+    <t>Check Planos  OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803783305046</t>
+  </si>
+  <si>
+    <t>1216803855236096</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Alabe OT 4381 ,Recepcion Rodete OT 4381 ,Recepcion motor OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803855236108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Alabe OT 4381 </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803855244569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Rodete OT 4381 </t>
+  </si>
+  <si>
+    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega:,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216803882710950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion motor OT 4381 </t>
+  </si>
+  <si>
+    <t>1216803961866106</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje Rodete OT 4381,Montaje motor OT 4381,Montaje Alabe OT 4381 ,Revestimiento OT 4381</t>
+  </si>
+  <si>
+    <t>1216803961866118</t>
+  </si>
+  <si>
+    <t>Revestimiento OT 4381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje:,Montaje Alabe OT 4381 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216803961773659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Check Planos  OT 4381 </t>
-  </si>
-  <si>
-    <t>Control de calidad Armado OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803882614137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Control de calidad Armado OT 4381 </t>
-  </si>
-  <si>
-    <t>1216804003009895</t>
-  </si>
-  <si>
-    <t>Check Planos  OT 4381 ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803783305046</t>
-  </si>
-  <si>
-    <t>1216803855236096</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Alabe OT 4381 ,Recepcion Rodete OT 4381 ,Recepcion motor OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803855236108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Alabe OT 4381 </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803855244569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Rodete OT 4381 </t>
-  </si>
-  <si>
-    <t>OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,Bodega:,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216803882710950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion motor OT 4381 </t>
-  </si>
-  <si>
-    <t>1216803961866106</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje Rodete OT 4381,Montaje motor OT 4381,Montaje Alabe OT 4381 ,Revestimiento OT 4381</t>
-  </si>
-  <si>
-    <t>1216803961866118</t>
-  </si>
-  <si>
-    <t>Revestimiento OT 4381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje:,Montaje Alabe OT 4381 </t>
   </si>
   <si>
     <t>1216803961867347</t>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46274.16866657407</v>
+        <v>46275.146271840276</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>197</v>
@@ -4883,8 +4883,8 @@
       <c r="R58" s="5">
         <v>46274</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>198</v>
+      <c r="S58" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4895,7 +4895,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B59" s="9">
         <v>46225.862089999995</v>
@@ -4935,10 +4935,10 @@
         <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>201</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46225.86209783565</v>
@@ -4988,10 +4988,10 @@
         <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B61" s="9">
         <v>46225.86210570602</v>
@@ -5041,10 +5041,10 @@
         <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5054,7 +5054,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46225.86216362269</v>
@@ -5097,7 +5097,7 @@
         <v>149</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5107,7 +5107,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B63" s="9">
         <v>46225.86219280092</v>
@@ -5117,7 +5117,7 @@
         <v>46225.86232971065</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>25</v>
@@ -5141,7 +5141,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5154,7 +5154,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B64" s="5">
         <v>46225.86219668981</v>
@@ -5164,7 +5164,7 @@
         <v>46232.19127755787</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5191,13 +5191,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q64" s="5">
         <v>46231</v>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B65" s="9">
         <v>46225.86220582176</v>
@@ -5227,7 +5227,7 @@
         <v>46232.19127729167</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5254,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="9">
         <v>46231</v>
@@ -5280,7 +5280,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5">
         <v>46225.86221482639</v>
@@ -5290,7 +5290,7 @@
         <v>46232.19127710648</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5317,13 +5317,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5343,7 +5343,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B67" s="9">
         <v>46225.862222800926</v>
@@ -5353,7 +5353,7 @@
         <v>46232.60338638889</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>25</v>
@@ -5377,7 +5377,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>26</v>
@@ -5390,7 +5390,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B68" s="5">
         <v>46225.862226516205</v>
@@ -5400,7 +5400,7 @@
         <v>46274.146724861115</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5427,13 +5427,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>147</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46281</v>
@@ -5442,7 +5442,7 @@
         <v>46275</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -5490,7 +5490,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>149</v>
@@ -5543,7 +5543,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>149</v>
@@ -5596,7 +5596,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>149</v>
@@ -5649,7 +5649,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>149</v>
@@ -5702,7 +5702,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>234</v>
@@ -5969,7 +5969,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>246</v>
@@ -6244,13 +6244,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>257</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q83" s="9">
         <v>46288</v>
@@ -6519,7 +6519,7 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>147</v>
@@ -6794,7 +6794,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>277</v>
